--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6a76764cce3947c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R9d22225f397247ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R0af2e7e57c7841ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Rfe197704588b407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R5770446506134bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rfe43f790f4e440c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R50de69e4a00845ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rc431ed6acecf472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Re77445de55f9467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rc4e6b9042f9d40d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Rd41103710ae04479"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rd4401862e0c2410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3f88de69d3fd4adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R6366393978774324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdf40a27bb0ee447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rd8251a602ccd4988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R4a83e3e982444e99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R877e0a17a2394029"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rd82456a26c294b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R564ba404d5e44b57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R646f39df2df34665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rf21b1a01c7f44c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R0eed115a7b414357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R5575485924e54da7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Ra779a0d4bc7a4339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R902a1cce89a14c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3f4173ef22564a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Red7c9e3ad5dd4459"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,7 +3488,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R140eae9446e14497"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde90675731c44577"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3518,7 +3518,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38f8bcdea713437e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R822a941b3c684f23"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3545,7 +3545,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4282137981d14ea1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re2cee3c1ff8448a9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3577,7 +3577,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb28f979f983d46ff"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R99c093b244da44ee"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3609,7 +3609,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra95d6fc3d9cf4a49"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7b9151166464413e"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4017,7 +4017,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="504" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="505"/>
       <x:c r="E4" s="504"/>
@@ -4457,7 +4457,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23b8d6bd5e124d1c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67f18ce58d834923"/>
 </x:worksheet>
 </file>
 
@@ -10333,7 +10333,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b0a78bcb0544b4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6d8a1b651e04c69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10351,7 +10351,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21a4d499296e4375"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0d10f98845443e"/>
 </x:worksheet>
 </file>
 
@@ -10368,7 +10368,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7fc2917860d4761"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42cb375b4ff641a6"/>
 </x:worksheet>
 </file>
 
@@ -10385,7 +10385,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc307ba66ecbc475b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e5581b4e4d45cf"/>
 </x:worksheet>
 </file>
 
@@ -13020,7 +13020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1053cbe5bad423f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1da1ee939fa4265"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14648,7 +14648,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabc5a3e01d64ded"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7894036867b64bfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17240,7 +17240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d4c250c4a4b45d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d22400ba07f45b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22976,7 +22976,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R468448d673eb4eaa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf476d7591ff54d9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25237,7 +25237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c4b9225a1648ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2b01def7ae34c99"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27615,7 +27615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ba84c0238b46cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3bce9b539ef4d4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rdf40a27bb0ee447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rd8251a602ccd4988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R4a83e3e982444e99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R877e0a17a2394029"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="Rd82456a26c294b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="R564ba404d5e44b57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R646f39df2df34665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rf21b1a01c7f44c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R0eed115a7b414357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R5575485924e54da7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Ra779a0d4bc7a4339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R902a1cce89a14c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3f4173ef22564a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Red7c9e3ad5dd4459"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6a76764cce3947c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R9d22225f397247ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R0af2e7e57c7841ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Rfe197704588b407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R5770446506134bdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rfe43f790f4e440c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R50de69e4a00845ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rc431ed6acecf472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="Re77445de55f9467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rc4e6b9042f9d40d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Rd41103710ae04479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Rd4401862e0c2410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R3f88de69d3fd4adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R6366393978774324"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3488,7 +3488,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rde90675731c44577"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R140eae9446e14497"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3518,7 +3518,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R822a941b3c684f23"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38f8bcdea713437e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3545,7 +3545,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re2cee3c1ff8448a9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4282137981d14ea1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3577,7 +3577,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R99c093b244da44ee"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb28f979f983d46ff"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3609,7 +3609,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7b9151166464413e"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra95d6fc3d9cf4a49"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4017,7 +4017,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="504" t="str">
-        <x:v>AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="505"/>
       <x:c r="E4" s="504"/>
@@ -4457,7 +4457,7 @@
     <x:mergeCell ref="A1:H1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67f18ce58d834923"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23b8d6bd5e124d1c"/>
 </x:worksheet>
 </file>
 
@@ -10333,7 +10333,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6d8a1b651e04c69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b0a78bcb0544b4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10351,7 +10351,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0d10f98845443e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21a4d499296e4375"/>
 </x:worksheet>
 </file>
 
@@ -10368,7 +10368,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42cb375b4ff641a6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7fc2917860d4761"/>
 </x:worksheet>
 </file>
 
@@ -10385,7 +10385,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e5581b4e4d45cf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc307ba66ecbc475b"/>
 </x:worksheet>
 </file>
 
@@ -13020,7 +13020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1da1ee939fa4265"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1053cbe5bad423f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14648,7 +14648,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7894036867b64bfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reabc5a3e01d64ded"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17240,7 +17240,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d22400ba07f45b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d4c250c4a4b45d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22976,7 +22976,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf476d7591ff54d9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R468448d673eb4eaa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25237,7 +25237,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2b01def7ae34c99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c4b9225a1648ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27615,7 +27615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3bce9b539ef4d4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ba84c0238b46cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,21 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R77e546bd551747f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R72c56880243946a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R343b47ed007641ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re51808aa45cf4b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R0948e652aa014d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rbaa46638046740a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R7174d7d934f9473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R182074a894124667"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R2229a117b6834a4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rce3762c9891c45fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Ra2fa7a0aeb694d07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R6f3783afcf884537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Re66316986d6542dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rc1a43a12869243b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R1086a3a2359e4666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf752a38e741e4ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rf4dea3fe598247c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ree7407ddcc9d495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re123dc68b8e54d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R25dbb5060e8d4f68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ref185e2fb00f45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R28247057f66345cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R24e01eec4e694e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R8b3a01cfe48c4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rbb9dec15eb974821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R7191b27c2f6c45ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Ra6c8ff1ca08e4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R78bcfe32913f407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rb0b681b17de44624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R15aff244e05b43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R2c52d43831674a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="Rd080fd4cbbd648ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5b5097dc83894957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Raf39a401fa784812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rbf332aa915b043c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R2b39b65a7ccf4c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R20007ec591744bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R8cbf6de426b54b34"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -302,7 +310,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -315,10 +323,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -328,7 +336,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>99.647</x:v>
+        <x:v>99.613</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Populated purity results</x:v>
@@ -341,7 +349,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14"/>
@@ -352,7 +360,7 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="14"/>
@@ -363,7 +371,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -374,10 +382,10 @@
         <x:v>Labs Used</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D9" s="14"/>
       <x:c r="E9" s="14"/>
@@ -387,7 +395,7 @@
         <x:v>Latest COA Date</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C10" s="14"/>
       <x:c r="D10" s="14"/>
@@ -419,129 +427,135 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>COA-0036</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D13" s="14" t="n">
-        <x:v>99.82</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Clear</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>GHK-Cu</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D14" s="14" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>White</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>COA-0024</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D15" s="14" t="n">
-        <x:v>99.86</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Blue</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D16" s="14" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D17" s="14" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="14" t="str">
-        <x:v>COA-0001</x:v>
-      </x:c>
-      <x:c r="B18" s="14"/>
-      <x:c r="C18" s="14"/>
-      <x:c r="D18" s="14"/>
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B18" s="14" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="D18" s="14" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="14" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="D19" s="14" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D20" s="14" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -549,16 +563,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D21" s="14" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -566,16 +580,16 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D22" s="14" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -583,16 +597,16 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D23" s="14" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -600,16 +614,16 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D24" s="14" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -617,16 +631,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D25" s="14" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -634,16 +648,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D26" s="14" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -651,16 +665,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>COA-0028</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>BPC/TB Blend</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D27" s="14" t="n">
-        <x:v>99.81</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -668,16 +682,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D28" s="14" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -685,16 +699,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D29" s="14" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -702,16 +716,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D30" s="14" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.055</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -719,54 +733,44 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0011</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D31" s="14" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.04</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="D32" s="14" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="14" t="str">
-        <x:v>COA-0034</x:v>
-      </x:c>
-      <x:c r="B33" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
-      </x:c>
-      <x:c r="C33" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="D33" s="14" t="n">
-        <x:v>99.747</x:v>
-      </x:c>
-      <x:c r="E33" s="14" t="str">
-        <x:v>Purple</x:v>
-      </x:c>
+      <x:c r="A33" s="14"/>
+      <x:c r="B33" s="14"/>
+      <x:c r="C33" s="14"/>
+      <x:c r="D33" s="14"/>
+      <x:c r="E33" s="14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -853,7 +857,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>All records from COA Database</x:v>
@@ -1015,7 +1019,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>99.647</x:v>
+        <x:v>99.613</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -5555,6 +5559,586 @@
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-237183 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-442015 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-538821 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-654610 - SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7797,7 +8381,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Pass</x:v>
@@ -7865,7 +8449,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Pass</x:v>
@@ -7933,7 +8517,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8001,7 +8585,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8088,6 +8672,1130 @@
       </x:c>
       <x:c r="V37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Report reviewed</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-697297 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>White</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-822844 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/COA RPT-2026-932680 - SteriGenix.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Report/Task #</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>Test Date</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>assets/coa/Elor5-20260731S0925_report.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8736,43 +10444,43 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>COA-0035</x:v>
+        <x:v>COA-0041</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
         <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
       <x:c r="E15" s="14" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F15" s="14" t="n">
-        <x:v>50.75</x:v>
+        <x:v>51.34</x:v>
       </x:c>
       <x:c r="G15" s="16" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.026800000000000067</x:v>
       </x:c>
       <x:c r="H15" s="18" t="n">
-        <x:v>99.77</x:v>
+        <x:v>99.78</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J15" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
-      </x:c>
-      <x:c r="K15" s="14" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K15" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L15" s="14" t="str">
-        <x:v>Clear/Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M15" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8780,43 +10488,43 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
-        <x:v>COA-0034</x:v>
+        <x:v>COA-0035</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Regenerative / Skin</x:v>
       </x:c>
       <x:c r="E16" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F16" s="14" t="n">
-        <x:v>15.59</x:v>
+        <x:v>50.75</x:v>
       </x:c>
       <x:c r="G16" s="16" t="n">
-        <x:v>0.03933333333333333</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="H16" s="18" t="n">
-        <x:v>99.747</x:v>
+        <x:v>99.77</x:v>
       </x:c>
       <x:c r="I16" s="14" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="L16" s="14" t="str">
-        <x:v>Purple</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="M16" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -8824,7 +10532,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0034</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8836,31 +10544,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F17" s="14" t="n">
-        <x:v>16.18</x:v>
+        <x:v>15.59</x:v>
       </x:c>
       <x:c r="G17" s="16" t="n">
-        <x:v>0.07866666666666665</x:v>
+        <x:v>0.03933333333333333</x:v>
       </x:c>
       <x:c r="H17" s="18" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.747</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K17" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K17" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Purple</x:v>
       </x:c>
       <x:c r="M17" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
+        <x:v>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8868,7 +10576,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8877,34 +10585,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E18" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F18" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="G18" s="16" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.07866666666666665</x:v>
       </x:c>
       <x:c r="H18" s="18" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="I18" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J18" s="14" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K18" s="14" t="n">
-        <x:v>46133</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L18" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M18" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -8912,7 +10620,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -8921,13 +10629,13 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>46.6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
         <x:v>99.7</x:v>
@@ -8939,16 +10647,16 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K19" s="14" t="n">
-        <x:v>46106</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -8956,43 +10664,43 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>6.63</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
-        <x:v>0.326</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H20" s="18" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I20" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J20" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K20" s="14" t="n">
-        <x:v>46174</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -9000,43 +10708,43 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>15.53</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G21" s="16" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H21" s="18" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K21" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K21" s="14" t="n">
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -9044,25 +10752,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
-        <x:v>33.24</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H22" s="18" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -9070,17 +10778,17 @@
       <x:c r="J22" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K22" s="14" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M22" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -9088,43 +10796,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
-        <x:v>12.19</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G23" s="16" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H23" s="18" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K23" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K23" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -9132,10 +10840,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -9144,31 +10852,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
-        <x:v>33.77</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G24" s="16" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H24" s="18" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -9176,43 +10884,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
-        <x:v>42.53</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G25" s="16" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H25" s="18" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -9220,7 +10928,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9232,31 +10940,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
-        <x:v>33.31</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H26" s="18" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M26" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -9264,43 +10972,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F27" s="14" t="n">
-        <x:v>11.8</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H27" s="18" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K27" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -9308,7 +11016,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9316,31 +11024,35 @@
       <x:c r="D28" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E28" s="14"/>
+      <x:c r="E28" s="14" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="F28" s="14" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G28" s="16"/>
+        <x:v>42.53</x:v>
+      </x:c>
+      <x:c r="G28" s="16" t="n">
+        <x:v>0.06325</x:v>
+      </x:c>
       <x:c r="H28" s="18" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
-      </x:c>
-      <x:c r="K28" s="14" t="n">
-        <x:v>46146</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -9348,7 +11060,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9357,16 +11069,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F29" s="14" t="n">
-        <x:v>17.93</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G29" s="16" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H29" s="18" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -9374,17 +11086,17 @@
       <x:c r="J29" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K29" s="14" t="n">
-        <x:v>46175</x:v>
+      <x:c r="K29" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -9392,43 +11104,43 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="14" t="n">
-        <x:v>21.4</x:v>
+        <x:v>10.09</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.06999999999999999</x:v>
+        <x:v>0.008999999999999985</x:v>
       </x:c>
       <x:c r="H30" s="18" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J30" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -9436,34 +11148,34 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
-        <x:v>45.03</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="G31" s="16" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.1800000000000001</x:v>
       </x:c>
       <x:c r="H31" s="18" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K31" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K31" s="14" t="n">
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9472,7 +11184,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -9480,7 +11192,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -9488,26 +11200,22 @@
       <x:c r="D32" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E32" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="E32" s="14"/>
       <x:c r="F32" s="14" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G32" s="16"/>
       <x:c r="H32" s="18" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J32" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="K32" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9516,7 +11224,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -9524,34 +11232,34 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D33" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
-        <x:v>11.38</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H33" s="18" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K33" s="14" t="n">
-        <x:v>46155</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9560,7 +11268,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -9568,34 +11276,34 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D34" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E34" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F34" s="14" t="n">
-        <x:v>11.17</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G34" s="16" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H34" s="18" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J34" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K34" s="14" t="n">
-        <x:v>46155</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -9604,7 +11312,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -9612,10 +11320,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D35" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
@@ -9624,31 +11332,467 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="14" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="G35" s="16" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H35" s="18" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I35" s="14" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J35" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K35" s="14" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L35" s="14" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="M35" s="14" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="N35" s="14" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>COA-0029</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>45.03</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>0.12575</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>99.39</x:v>
+      </x:c>
+      <x:c r="I36" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J36" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K36" t="str">
+        <x:v>2026-06-15</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M36" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N36" t="str">
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>COA-0002</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>99.369</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J37" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K37" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M37" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N37" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>COA-0016</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>11.38</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.1380000000000001</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.085</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L41" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>TB-500 / TB4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>COA-0014</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>11.17</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L42" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>MS10 / MOTS-C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>COA-0011</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
         <x:v>10.47</x:v>
       </x:c>
-      <x:c r="G35" s="16" t="n">
+      <x:c r="G43" t="n">
         <x:v>0.04700000000000006</x:v>
       </x:c>
-      <x:c r="H35" s="18" t="n">
+      <x:c r="H43" t="n">
         <x:v>99.04</x:v>
       </x:c>
-      <x:c r="I35" s="14" t="str">
+      <x:c r="I43" t="str">
         <x:v>On label</x:v>
       </x:c>
-      <x:c r="J35" s="14" t="str">
+      <x:c r="J43" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
-      <x:c r="K35" s="14" t="n">
+      <x:c r="K43" t="n">
         <x:v>46155</x:v>
       </x:c>
-      <x:c r="L35" s="14" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="M35" s="14" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="N35" s="14" t="str">
+      <x:c r="L43" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
         <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H44"/>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L44" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H45"/>
+      <x:c r="I45" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11891,7 +14035,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Pass</x:v>
@@ -11959,7 +14103,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Pass</x:v>
@@ -12027,7 +14171,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>Local image: assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Pass</x:v>
@@ -12095,13 +14239,13 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
       </x:c>
       <x:c r="R36" s="14" t="str">
-        <x:v>Unique Freedom Diagnostics GHK-Cu 50mg COA; no exact duplicate by compound/lab/date/content.</x:v>
+        <x:v>Append-only: independent test record retained; never overwrite or remove records based only on peptide name.</x:v>
       </x:c>
       <x:c r="S36" s="14" t="str">
         <x:v>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</x:v>
@@ -12182,6 +14326,550 @@
       </x:c>
       <x:c r="V37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Report reviewed</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14081,7 +16769,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14143,7 +16831,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14205,7 +16893,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14267,7 +16955,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -14329,7 +17017,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P33" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="Q33" s="14" t="str">
         <x:v>Black</x:v>
@@ -14391,7 +17079,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P34" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="Q34" s="14" t="str">
         <x:v>Blue</x:v>
@@ -14453,7 +17141,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P35" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="Q35" s="14" t="str">
         <x:v>Purple</x:v>
@@ -14515,7 +17203,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Clear/Transparent</x:v>
@@ -14577,7 +17265,7 @@
         <x:v>Trio2607170250</x:v>
       </x:c>
       <x:c r="P37" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>Freedom Diagnostics COA PDF</x:v>
       </x:c>
       <x:c r="Q37" s="14" t="str">
         <x:v>Yellow</x:v>
@@ -14590,6 +17278,502 @@
       </x:c>
       <x:c r="T37" s="14" t="str">
         <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="J38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="P38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="J39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="P39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="J40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="P40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="J41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="P41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="J42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="P42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="J43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="P43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="M44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="P44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="J45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16448,7 +19632,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16513,7 +19697,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16578,7 +19762,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16643,7 +19827,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16708,7 +19892,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G33" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-14-31.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Semaglutide 15mg)</x:v>
       </x:c>
       <x:c r="H33" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16773,7 +19957,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G34" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-34-37.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 30mg)</x:v>
       </x:c>
       <x:c r="H34" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16838,7 +20022,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G35" s="14" t="str">
-        <x:v>assets/coa/photo_2026-07-04_22-35-21.jpg</x:v>
+        <x:v>Local image: No local image on file (Kovera COA, Tirzepatide 15mg)</x:v>
       </x:c>
       <x:c r="H35" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16903,7 +20087,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>assets/coa/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
+        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>Yes</x:v>
@@ -16968,7 +20152,7 @@
         <x:v>Trio2607170250</x:v>
       </x:c>
       <x:c r="G37" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>Freedom Diagnostics COA PDF</x:v>
       </x:c>
       <x:c r="H37" s="14" t="str">
         <x:v>Yes</x:v>
@@ -17011,6 +20195,526 @@
       </x:c>
       <x:c r="U37" s="14" t="str">
         <x:v>Yellow flip-off cap with silver aluminum crimp, based on the vial image shown on page 1 of the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E38" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="F38" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="G38" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H38" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="N38" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O38" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="P38" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q38" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R38" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S38" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E39" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="F39" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="G39" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H39" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="N39" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O39" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="P39" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q39" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R39" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S39" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E40" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="F40" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="N40" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O40" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="P40" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q40" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R40" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S40" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E41" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="F41" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="G41" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H41" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="N41" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O41" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="P41" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q41" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R41" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S41" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E42" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="F42" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="G42" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H42" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="M42" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="N42" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O42" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="P42" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q42" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R42" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S42" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="K43" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="M43" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="N43" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O43" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="P43" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q43" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R43" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S43" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="E44" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="F44" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="G44" t="str">
+        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+      </x:c>
+      <x:c r="H44" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="M44" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="N44" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O44" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="P44" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="Q44" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R44" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+      <x:c r="S44" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="E45" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="F45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="O45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="P45" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="Q45" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R45" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+      <x:c r="S45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17052,63 +20756,67 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>ADAMAX</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
         <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Clear Green</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="14" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>Gold</x:v>
-      </x:c>
-      <x:c r="E3" s="14"/>
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Cosmetic / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
         <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Gray</x:v>
-      </x:c>
-      <x:c r="E4" s="14"/>
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
         <x:v>Janoshik</x:v>
@@ -17117,80 +20825,104 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear Green</x:v>
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Clear/Transparent</x:v>
       </x:c>
       <x:c r="E6" s="14"/>
       <x:c r="F6" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>MOTS-C</x:v>
-      </x:c>
-      <x:c r="B7" s="14"/>
+        <x:v>CJC-1295 No DAC</x:v>
+      </x:c>
+      <x:c r="B7" s="14" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
       <x:c r="C7" s="14"/>
-      <x:c r="D7" s="14"/>
+      <x:c r="D7" s="14" t="str">
+        <x:v>Gold</x:v>
+      </x:c>
       <x:c r="E7" s="14"/>
       <x:c r="F7" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>Retatrutide</x:v>
-      </x:c>
-      <x:c r="B8" s="14"/>
+        <x:v>Cagrilintide</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
       <x:c r="C8" s="14"/>
-      <x:c r="D8" s="14"/>
+      <x:c r="D8" s="14" t="str">
+        <x:v>Gray</x:v>
+      </x:c>
       <x:c r="E8" s="14"/>
-      <x:c r="F8" s="14"/>
+      <x:c r="F8" s="14" t="str">
+        <x:v>Metabolic / Fat Loss</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>SS-31</x:v>
-      </x:c>
-      <x:c r="B9" s="14"/>
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="B9" s="14" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
       <x:c r="C9" s="14"/>
-      <x:c r="D9" s="14"/>
+      <x:c r="D9" s="14" t="str">
+        <x:v>Green</x:v>
+      </x:c>
       <x:c r="E9" s="14"/>
-      <x:c r="F9" s="14"/>
+      <x:c r="F9" s="14" t="str">
+        <x:v>Metabolic / Mito</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="B10" s="14"/>
       <x:c r="C10" s="14"/>
-      <x:c r="D10" s="14"/>
+      <x:c r="D10" s="14" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
       <x:c r="E10" s="14"/>
-      <x:c r="F10" s="14"/>
+      <x:c r="F10" s="14" t="str">
+        <x:v>Other</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="14"/>
-      <x:c r="D11" s="14"/>
+      <x:c r="D11" s="14" t="str">
+        <x:v>Purple</x:v>
+      </x:c>
       <x:c r="E11" s="14"/>
-      <x:c r="F11" s="14"/>
+      <x:c r="F11" s="14" t="str">
+        <x:v>Regenerative / Skin</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
@@ -17198,39 +20930,91 @@
       </x:c>
       <x:c r="B12" s="14"/>
       <x:c r="C12" s="14"/>
-      <x:c r="D12" s="14"/>
+      <x:c r="D12" s="14" t="str">
+        <x:v>Red</x:v>
+      </x:c>
       <x:c r="E12" s="14"/>
-      <x:c r="F12" s="14"/>
+      <x:c r="F12" s="14" t="str">
+        <x:v>Research Peptide</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="14"/>
+      <x:c r="A13" s="14" t="str">
+        <x:v>KPV</x:v>
+      </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="14"/>
       <x:c r="D13" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="E13" s="14"/>
       <x:c r="F13" s="14"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="14"/>
+      <x:c r="A14" s="14" t="str">
+        <x:v>MOTS-C</x:v>
+      </x:c>
       <x:c r="B14" s="14"/>
       <x:c r="C14" s="14"/>
-      <x:c r="D14" s="14"/>
-      <x:c r="E14" s="14" t="str">
-        <x:v>Silver</x:v>
-      </x:c>
+      <x:c r="D14" s="14" t="str">
+        <x:v>Transparent</x:v>
+      </x:c>
+      <x:c r="E14" s="14"/>
       <x:c r="F14" s="14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="14"/>
+      <x:c r="A15" s="14" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="14"/>
-      <x:c r="D15" s="14"/>
+      <x:c r="D15" s="14" t="str">
+        <x:v>White</x:v>
+      </x:c>
       <x:c r="E15" s="14"/>
-      <x:c r="F15" s="14" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
-      </x:c>
+      <x:c r="F15" s="14"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>SS-31</x:v>
+      </x:c>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf752a38e741e4ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rf4dea3fe598247c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ree7407ddcc9d495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re123dc68b8e54d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R25dbb5060e8d4f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ref185e2fb00f45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R28247057f66345cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R24e01eec4e694e4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R8b3a01cfe48c4145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rbb9dec15eb974821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R7191b27c2f6c45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Ra6c8ff1ca08e4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R78bcfe32913f407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rb0b681b17de44624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R15aff244e05b43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R2c52d43831674a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="Rd080fd4cbbd648ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5b5097dc83894957"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Raf39a401fa784812"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rbf332aa915b043c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R2b39b65a7ccf4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R20007ec591744bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R8cbf6de426b54b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2e87ca495a7d4fdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R0ce4da82a3fb4089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R00534e303ef240ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R9608f5f476c44cc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R5b5ac10f618b4e69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rb9fa7c0d7ff342a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R1b2c295b388846af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Re6d95b7662b646bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R56c390ae545245ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R7d3d680b6372401f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Rdeeeba0222914483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R69babcd085824833"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R9f9fab07a9fb40f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R24111491821948ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R43538f9215a14812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R485efea0e9024b89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R81b097d104fd4789"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R6c12e678c0c1463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R2a3a0f926b5548e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="R231c8e804c0a4155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R6f2dd20a8d224da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R443308713a254ea0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R1059db03a43e4238"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,29 +2,29 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2e87ca495a7d4fdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R0ce4da82a3fb4089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="R00534e303ef240ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R9608f5f476c44cc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R5b5ac10f618b4e69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rb9fa7c0d7ff342a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R1b2c295b388846af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Re6d95b7662b646bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R56c390ae545245ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R7d3d680b6372401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="Rdeeeba0222914483"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R69babcd085824833"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R9f9fab07a9fb40f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="R24111491821948ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R43538f9215a14812"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R485efea0e9024b89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R81b097d104fd4789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R6c12e678c0c1463b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R2a3a0f926b5548e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="R231c8e804c0a4155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R6f2dd20a8d224da9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R443308713a254ea0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R1059db03a43e4238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf752a38e741e4ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rf4dea3fe598247c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ree7407ddcc9d495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re123dc68b8e54d03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R25dbb5060e8d4f68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ref185e2fb00f45be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R28247057f66345cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R24e01eec4e694e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R8b3a01cfe48c4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rbb9dec15eb974821"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R7191b27c2f6c45ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Ra6c8ff1ca08e4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R78bcfe32913f407c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rb0b681b17de44624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R15aff244e05b43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R2c52d43831674a2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="Rd080fd4cbbd648ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5b5097dc83894957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Raf39a401fa784812"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rbf332aa915b043c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R2b39b65a7ccf4c4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R20007ec591744bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R8cbf6de426b54b34"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -2,29 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rf752a38e741e4ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="Rf4dea3fe598247c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Ree7407ddcc9d495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="Re123dc68b8e54d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R25dbb5060e8d4f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Ref185e2fb00f45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="R28247057f66345cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="R24e01eec4e694e4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R8b3a01cfe48c4145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="Rbb9dec15eb974821"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R7191b27c2f6c45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="Ra6c8ff1ca08e4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="R78bcfe32913f407c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Rb0b681b17de44624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R15aff244e05b43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R2c52d43831674a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="Rd080fd4cbbd648ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R5b5097dc83894957"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="Raf39a401fa784812"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Rbf332aa915b043c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R2b39b65a7ccf4c4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R20007ec591744bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R8cbf6de426b54b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Reeb0fa714e0c44f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Database" sheetId="2" r:id="R7922c2f893674a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purity Rankings" sheetId="3" r:id="Rb184cbff393a4ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Batch History" sheetId="4" r:id="R3cf3f5fbe10a4c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lab Match" sheetId="5" r:id="R6d300acf81c1469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventory" sheetId="6" r:id="Rcdef4b2a823542c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificates" sheetId="7" r:id="Rf901a3dc714a4da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="8" r:id="Rdcbf0d3bd23a4e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="9" r:id="R91f7bd3644d64308"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA Status" sheetId="10" r:id="R799cd7fa81f64fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Half-Life Reference" sheetId="11" r:id="R6e70528a501e4839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta30_Kovera" sheetId="12" r:id="R29dccaaa95f145d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Reta40_Kovera" sheetId="13" r:id="Re20cd7c284dc4497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_Adamax_SteriGenix" sheetId="14" r:id="Re0d3370775d04442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_KLOW80_Freedom" sheetId="15" r:id="R7869152daa4c46f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0037" sheetId="16" r:id="R226132d664874399"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0038" sheetId="17" r:id="R8908573c6b6a479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0039" sheetId="18" r:id="R854d901e9a6d4bbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0040" sheetId="19" r:id="R01576f9a2d394744"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0041" sheetId="20" r:id="Re919ac1f1197456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0042" sheetId="21" r:id="R38667beed6a74424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0043" sheetId="22" r:id="R8d2b0c7fc0334318"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0044" sheetId="23" r:id="R03749e5be4ff4074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0045" sheetId="24" r:id="Rd94a466b5fb0439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0046" sheetId="25" r:id="Ra54493c7e90148d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -39,7 +41,7 @@
     <x:numFmt numFmtId="200" formatCode="0.00%"/>
     <x:numFmt numFmtId="201" formatCode="0.000"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -48,6 +50,11 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -71,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -119,6 +126,11 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -170,9 +182,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -310,7 +322,7 @@
         <x:v>Total COA Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>Synced from COA Database</x:v>
@@ -323,10 +335,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -336,7 +348,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>99.613</x:v>
+        <x:v>99.614</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Populated purity results</x:v>
@@ -349,7 +361,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14"/>
@@ -371,7 +383,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14"/>
@@ -382,10 +394,10 @@
         <x:v>Labs Used</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D9" s="14"/>
       <x:c r="E9" s="14"/>
@@ -546,16 +558,16 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="14" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="D20" s="14" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -563,16 +575,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D21" s="14" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -580,33 +592,33 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D22" s="14" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="14" t="str">
-        <x:v>COA-0023</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D23" s="14" t="n">
-        <x:v>99.731</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -614,16 +626,16 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="14" t="str">
-        <x:v>COA-0022</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
         <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="D24" s="14" t="n">
-        <x:v>99.825</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="E24" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -631,16 +643,16 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="14" t="str">
-        <x:v>COA-0021</x:v>
+        <x:v>COA-0023</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D25" s="14" t="n">
-        <x:v>99.897</x:v>
+        <x:v>99.731</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -648,16 +660,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="14" t="str">
-        <x:v>COA-0012</x:v>
+        <x:v>COA-0022</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>AOD-9604</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D26" s="14" t="n">
-        <x:v>99.883</x:v>
+        <x:v>99.825</x:v>
       </x:c>
       <x:c r="E26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -665,16 +677,16 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0021</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D27" s="14" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.897</x:v>
       </x:c>
       <x:c r="E27" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -682,16 +694,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="14" t="str">
-        <x:v>COA-0019</x:v>
+        <x:v>COA-0012</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>AOD-9604</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D28" s="14" t="n">
-        <x:v>99.95</x:v>
+        <x:v>99.883</x:v>
       </x:c>
       <x:c r="E28" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -699,16 +711,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="14" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D29" s="14" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="E29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -716,16 +728,16 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0019</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D30" s="14" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.95</x:v>
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -733,16 +745,16 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="14" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D31" s="14" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="E31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -750,16 +762,16 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="D32" s="14" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.055</x:v>
       </x:c>
       <x:c r="E32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -857,7 +869,7 @@
         <x:v>Total COA/Test Records</x:v>
       </x:c>
       <x:c r="B3" s="14" t="n">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>All records from COA Database</x:v>
@@ -884,10 +896,10 @@
         <x:v>Unique Peptides</x:v>
       </x:c>
       <x:c r="B4" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>ADAMAX, AOD-9604, BPC-157, BPC/TB Blend, CJC-1295 No DAC, Cagrilintide, GHK-Cu, KLOW 80mg, KPV, MOTS-C, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
+        <x:v>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="D4" s="14"/>
       <x:c r="E4" s="14"/>
@@ -911,7 +923,7 @@
         <x:v>Passed Records</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Pass/Fail column</x:v>
@@ -938,7 +950,7 @@
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="B6" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>Status column</x:v>
@@ -965,7 +977,7 @@
         <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="B7" s="14" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>Status column</x:v>
@@ -992,7 +1004,7 @@
         <x:v>On Label/Review</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
         <x:v>Status column</x:v>
@@ -1019,7 +1031,7 @@
         <x:v>Average Purity %</x:v>
       </x:c>
       <x:c r="B9" s="14" t="n">
-        <x:v>99.613</x:v>
+        <x:v>99.614</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>Based on populated purity values</x:v>
@@ -1046,10 +1058,10 @@
         <x:v>Unique Labs</x:v>
       </x:c>
       <x:c r="B10" s="14" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, Janoshik, Kovera Labs, SteriGenix, Testides</x:v>
+        <x:v>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="D10" s="14"/>
       <x:c r="E10" s="14"/>
@@ -1073,7 +1085,7 @@
         <x:v>Last Test Date</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
         <x:v>Most recent test date</x:v>
@@ -3281,6 +3293,596 @@
       </x:c>
       <x:c r="S49" s="14" t="str">
         <x:v>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>COA-0037</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>BPC-157 / TB-500 Blend</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>Healing / Recovery Blend</x:v>
+      </x:c>
+      <x:c r="D50" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E50" t="n">
+        <x:v>10.55</x:v>
+      </x:c>
+      <x:c r="F50" t="n">
+        <x:v>0.5500000000000007</x:v>
+      </x:c>
+      <x:c r="G50" t="n">
+        <x:v>0.05500000000000007</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>99.13</x:v>
+      </x:c>
+      <x:c r="I50" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J50" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K50" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L50" t="str">
+        <x:v>RPT-2026-237183</x:v>
+      </x:c>
+      <x:c r="M50" t="str">
+        <x:v>SGX-VP-2026-0728-G37</x:v>
+      </x:c>
+      <x:c r="N50" t="str">
+        <x:v>BB260725A</x:v>
+      </x:c>
+      <x:c r="O50" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P50" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q50" t="str">
+        <x:v>Red</x:v>
+      </x:c>
+      <x:c r="R50" t="str">
+        <x:v>Red flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S50" t="str">
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>COA-0038</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D51" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E51" t="n">
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="F51" t="n">
+        <x:v>0.08999999999999986</x:v>
+      </x:c>
+      <x:c r="G51" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
+      <x:c r="H51" t="n">
+        <x:v>99.52</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J51" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L51" t="str">
+        <x:v>RPT-2026-442015</x:v>
+      </x:c>
+      <x:c r="M51" t="str">
+        <x:v>SGX-VP-2026-0728-K72</x:v>
+      </x:c>
+      <x:c r="N51" t="str">
+        <x:v>TR260725A</x:v>
+      </x:c>
+      <x:c r="O51" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P51" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q51" t="str">
+        <x:v>Yellow</x:v>
+      </x:c>
+      <x:c r="R51" t="str">
+        <x:v>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S51" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>COA-0039</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>Semaglutide</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D52" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E52" t="n">
+        <x:v>5.07</x:v>
+      </x:c>
+      <x:c r="F52" t="n">
+        <x:v>0.07000000000000028</x:v>
+      </x:c>
+      <x:c r="G52" t="n">
+        <x:v>0.014000000000000058</x:v>
+      </x:c>
+      <x:c r="H52" t="n">
+        <x:v>99.32</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L52" t="str">
+        <x:v>RPT-2026-538821</x:v>
+      </x:c>
+      <x:c r="M52" t="str">
+        <x:v>SGX-VP-2026-0728-U17</x:v>
+      </x:c>
+      <x:c r="N52" t="str">
+        <x:v>SM260725A</x:v>
+      </x:c>
+      <x:c r="O52" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P52" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q52" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R52" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S52" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" t="str">
+        <x:v>COA-0040</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E53" t="n">
+        <x:v>5.13</x:v>
+      </x:c>
+      <x:c r="F53" t="n">
+        <x:v>0.1299999999999999</x:v>
+      </x:c>
+      <x:c r="G53" t="n">
+        <x:v>0.025999999999999978</x:v>
+      </x:c>
+      <x:c r="H53" t="n">
+        <x:v>99.57</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J53" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K53" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L53" t="str">
+        <x:v>RPT-2026-654610</x:v>
+      </x:c>
+      <x:c r="M53" t="str">
+        <x:v>SGX-VP-2026-0728-Z53</x:v>
+      </x:c>
+      <x:c r="N53" t="str">
+        <x:v>BC260725A</x:v>
+      </x:c>
+      <x:c r="O53" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P53" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q53" t="str">
+        <x:v>Green</x:v>
+      </x:c>
+      <x:c r="R53" t="str">
+        <x:v>Green flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S53" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>COA-0041</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>GHK-Cu</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Cosmetic / Recovery</x:v>
+      </x:c>
+      <x:c r="D54" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E54" t="n">
+        <x:v>51.34</x:v>
+      </x:c>
+      <x:c r="F54" t="n">
+        <x:v>1.3400000000000034</x:v>
+      </x:c>
+      <x:c r="G54" t="n">
+        <x:v>0.026800000000000067</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>99.78</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J54" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L54" t="str">
+        <x:v>RPT-2026-697297</x:v>
+      </x:c>
+      <x:c r="M54" t="str">
+        <x:v>SGX-VP-2026-0728-K16</x:v>
+      </x:c>
+      <x:c r="N54" t="str">
+        <x:v>CU260725A</x:v>
+      </x:c>
+      <x:c r="O54" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P54" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q54" t="str">
+        <x:v>Blue</x:v>
+      </x:c>
+      <x:c r="R54" t="str">
+        <x:v>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S54" t="str">
+        <x:v>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>COA-0042</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Ipamorelin</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Growth Hormone Support</x:v>
+      </x:c>
+      <x:c r="D55" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E55" t="n">
+        <x:v>5.17</x:v>
+      </x:c>
+      <x:c r="F55" t="n">
+        <x:v>0.16999999999999993</x:v>
+      </x:c>
+      <x:c r="G55" t="n">
+        <x:v>0.03399999999999999</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>99.34</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J55" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L55" t="str">
+        <x:v>RPT-2026-822844</x:v>
+      </x:c>
+      <x:c r="M55" t="str">
+        <x:v>SGX-VP-2026-0728-U21</x:v>
+      </x:c>
+      <x:c r="N55" t="str">
+        <x:v>IP260725A</x:v>
+      </x:c>
+      <x:c r="O55" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P55" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q55" t="str">
+        <x:v>White</x:v>
+      </x:c>
+      <x:c r="R55" t="str">
+        <x:v>White flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S55" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>COA-0043</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Retatrutide</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>GLP-1 / Weight</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E56" t="n">
+        <x:v>10.36</x:v>
+      </x:c>
+      <x:c r="F56" t="n">
+        <x:v>0.35999999999999943</x:v>
+      </x:c>
+      <x:c r="G56" t="n">
+        <x:v>0.03599999999999994</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>99.41</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J56" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="L56" t="str">
+        <x:v>RPT-2026-932680</x:v>
+      </x:c>
+      <x:c r="M56" t="str">
+        <x:v>SGX-VP-2026-0728-G60</x:v>
+      </x:c>
+      <x:c r="N56" t="str">
+        <x:v>RT260725A</x:v>
+      </x:c>
+      <x:c r="O56" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P56" t="str">
+        <x:v>Copper</x:v>
+      </x:c>
+      <x:c r="Q56" t="str">
+        <x:v>Clear</x:v>
+      </x:c>
+      <x:c r="R56" t="str">
+        <x:v>Clear flip-off cap with copper aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S56" t="str">
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>COA-0044</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Amylin / Weight</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E57" t="n">
+        <x:v>4.63</x:v>
+      </x:c>
+      <x:c r="F57" t="n">
+        <x:v>-0.3700000000000001</x:v>
+      </x:c>
+      <x:c r="G57" t="n">
+        <x:v>-0.07400000000000002</x:v>
+      </x:c>
+      <x:c r="H57" t="n">
+        <x:v>99.67</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>Underfilled</x:v>
+      </x:c>
+      <x:c r="J57" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="L57" t="str">
+        <x:v>Elor5-20260731S0925</x:v>
+      </x:c>
+      <x:c r="M57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="O57" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="Q57" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R57" t="str">
+        <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+      <x:c r="S57" t="str">
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E58" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F58" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G58" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H58" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J58" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="L58" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M58" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N58" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="O58" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P58" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="Q58" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R58" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+      <x:c r="S58" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E59" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G59" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H59" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J59" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K59" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="L59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="M59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N59" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O59" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="P59" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="Q59" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="R59" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="S59" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5558,7 +6160,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>assets/coa/KLOW80mg-02.pdf</x:v>
+        <x:v>assets/coa/documents/freedom-diagnostics/klow-80mg/KLOW80mg-02.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5703,7 +6305,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-237183 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5848,7 +6450,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-442015 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5993,7 +6595,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-538821 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6138,7 +6740,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-654610 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8109,7 +8711,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8177,7 +8779,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8245,7 +8847,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8313,7 +8915,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8585,7 +9187,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -8721,7 +9323,7 @@
         <x:v>BB260725A</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Pass</x:v>
@@ -8789,7 +9391,7 @@
         <x:v>TR260725A</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Pass</x:v>
@@ -8857,7 +9459,7 @@
         <x:v>SM260725A</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Pass</x:v>
@@ -8925,7 +9527,7 @@
         <x:v>BC260725A</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Pass</x:v>
@@ -8993,7 +9595,7 @@
         <x:v>CU260725A</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Pass</x:v>
@@ -9061,7 +9663,7 @@
         <x:v>IP260725A</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Pass</x:v>
@@ -9129,7 +9731,7 @@
         <x:v>RT260725A</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Pass</x:v>
@@ -9197,7 +9799,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Pass</x:v>
@@ -9216,6 +9818,142 @@
       </x:c>
       <x:c r="V45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9360,7 +10098,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-697297 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9505,7 +10243,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-822844 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9650,7 +10388,7 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/COA RPT-2026-932680 - SteriGenix.pdf</x:v>
+        <x:v>assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9795,7 +10533,401 @@
         <x:v>PDF</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>COA #</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>Accession #</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>ACC-2026-10918</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>Analysis Date</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>Date Received</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>Identity</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>Confirmed: CJC-1295 (HPLC-RTM)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12" t="str">
+        <x:v>Fentanyl Screen</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>Not Detected</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12" t="str">
+        <x:v>Sample Matrix</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>Lyophilized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12" t="str">
+        <x:v>Volume</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>3 mL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>COA/access identifiers are redacted in the supplied certificate image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>COA ID</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="12" t="str">
+        <x:v>Product</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="12" t="str">
+        <x:v>Compound Type</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="12" t="str">
+        <x:v>Lab</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="12" t="str">
+        <x:v>Certified</x:v>
+      </x:c>
+      <x:c r="B6" s="12" t="str">
+        <x:v>2026-07-29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="12" t="str">
+        <x:v>Report #</x:v>
+      </x:c>
+      <x:c r="B7" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="12" t="str">
+        <x:v>Verification Key</x:v>
+      </x:c>
+      <x:c r="B8" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="12" t="str">
+        <x:v>Batch/Lot</x:v>
+      </x:c>
+      <x:c r="B9" s="12" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="12" t="str">
+        <x:v>Labeled Qty (mg)</x:v>
+      </x:c>
+      <x:c r="B10" s="12" t="n">
+        <x:v>500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="12" t="str">
+        <x:v>Actual Content (mg)</x:v>
+      </x:c>
+      <x:c r="B11" s="12" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>Purity %</x:v>
+      </x:c>
+      <x:c r="B12" s="12" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B13" s="12" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>Identity</x:v>
+      </x:c>
+      <x:c r="B14" s="12" t="str">
+        <x:v>Confirmed: NAD+ (LC-MS)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>CAS Number</x:v>
+      </x:c>
+      <x:c r="B15" s="12" t="str">
+        <x:v>53-84-9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12" t="str">
+        <x:v>Molecular Formula</x:v>
+      </x:c>
+      <x:c r="B16" s="12" t="str">
+        <x:v>C21H27N7O14P2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12" t="str">
+        <x:v>Endotoxin Safety Screen</x:v>
+      </x:c>
+      <x:c r="B17" s="12" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12" t="str">
+        <x:v>Heavy Metals</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="str">
+        <x:v>Arsenic, Cadmium, Lead, Mercury: Negative</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="12" t="str">
+        <x:v>Vial 1</x:v>
+      </x:c>
+      <x:c r="B19" s="12" t="str">
+        <x:v>99.517% purity / 483.68 mg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="12" t="str">
+        <x:v>Vial 2</x:v>
+      </x:c>
+      <x:c r="B20" s="12" t="str">
+        <x:v>99.582% purity / 493.26 mg</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="12" t="str">
+        <x:v>Cap Color</x:v>
+      </x:c>
+      <x:c r="B21" s="12" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="12" t="str">
+        <x:v>Crimp Color</x:v>
+      </x:c>
+      <x:c r="B22" s="12" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="12" t="str">
+        <x:v>Closure Notes</x:v>
+      </x:c>
+      <x:c r="B23" s="12" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="12" t="str">
+        <x:v>PDF</x:v>
+      </x:c>
+      <x:c r="B24" s="12" t="str">
+        <x:v>assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10620,43 +11752,43 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>COA-0007</x:v>
+        <x:v>COA-0045</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
       <x:c r="E19" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="14" t="n">
-        <x:v>26</x:v>
+        <x:v>10.52</x:v>
       </x:c>
       <x:c r="G19" s="16" t="n">
-        <x:v>0.3</x:v>
+        <x:v>0.051999999999999956</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
-        <x:v>99.7</x:v>
+        <x:v>99.72</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J19" s="14" t="str">
-        <x:v>BT Labs</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="K19" s="14" t="n">
-        <x:v>46133</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L19" s="14" t="str">
-        <x:v>Royal Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M19" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>20 mg label; 130.1% potency</x:v>
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -10664,7 +11796,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>COA-0008</x:v>
+        <x:v>COA-0007</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
         <x:v>Tirzepatide</x:v>
@@ -10673,13 +11805,13 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E20" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="14" t="n">
-        <x:v>46.6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G20" s="16" t="n">
-        <x:v>0.165</x:v>
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="H20" s="18" t="n">
         <x:v>99.7</x:v>
@@ -10691,16 +11823,16 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K20" s="14" t="n">
-        <x:v>46106</x:v>
+        <x:v>46133</x:v>
       </x:c>
       <x:c r="L20" s="14" t="str">
-        <x:v>Gray</x:v>
+        <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="M20" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>40 mg label; 116.4% potency</x:v>
+        <x:v>20 mg label; 130.1% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10708,43 +11840,43 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>COA-0044</x:v>
+        <x:v>COA-0008</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>Amylin / Weight</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E21" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F21" s="14" t="n">
-        <x:v>4.63</x:v>
+        <x:v>46.6</x:v>
       </x:c>
       <x:c r="G21" s="16" t="n">
-        <x:v>-0.07400000000000002</x:v>
+        <x:v>0.165</x:v>
       </x:c>
       <x:c r="H21" s="18" t="n">
-        <x:v>99.67</x:v>
+        <x:v>99.7</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>Underfilled</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="K21" s="14" t="n">
-        <x:v>46234</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L21" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Gray</x:v>
       </x:c>
       <x:c r="M21" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+        <x:v>40 mg label; 116.4% potency</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -10752,34 +11884,34 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
-        <x:v>COA-0003</x:v>
+        <x:v>COA-0044</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Eloralintide</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Amylin / Weight</x:v>
       </x:c>
       <x:c r="E22" s="14" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F22" s="14" t="n">
-        <x:v>6.63</x:v>
+        <x:v>4.63</x:v>
       </x:c>
       <x:c r="G22" s="16" t="n">
-        <x:v>0.326</x:v>
+        <x:v>-0.07400000000000002</x:v>
       </x:c>
       <x:c r="H22" s="18" t="n">
-        <x:v>99.654</x:v>
+        <x:v>99.67</x:v>
       </x:c>
       <x:c r="I22" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Underfilled</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
       </x:c>
       <x:c r="K22" s="14" t="n">
-        <x:v>46174</x:v>
+        <x:v>46234</x:v>
       </x:c>
       <x:c r="L22" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -10788,7 +11920,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10796,43 +11928,43 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
-        <x:v>COA-0032</x:v>
+        <x:v>COA-0003</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E23" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="14" t="n">
-        <x:v>15.53</x:v>
+        <x:v>6.63</x:v>
       </x:c>
       <x:c r="G23" s="16" t="n">
-        <x:v>0.035333333333333335</x:v>
+        <x:v>0.326</x:v>
       </x:c>
       <x:c r="H23" s="18" t="n">
-        <x:v>99.642</x:v>
+        <x:v>99.654</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
         <x:v>Kovera Labs</x:v>
       </x:c>
-      <x:c r="K23" s="14" t="str">
-        <x:v>2026-07-03</x:v>
+      <x:c r="K23" s="14" t="n">
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="L23" s="14" t="str">
-        <x:v>Black</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M23" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -10840,28 +11972,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="14" t="str">
-        <x:v>COA-0033</x:v>
+        <x:v>COA-0032</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D24" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E24" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F24" s="14" t="n">
-        <x:v>33.24</x:v>
+        <x:v>15.53</x:v>
       </x:c>
       <x:c r="G24" s="16" t="n">
-        <x:v>0.10800000000000001</x:v>
+        <x:v>0.035333333333333335</x:v>
       </x:c>
       <x:c r="H24" s="18" t="n">
-        <x:v>99.6</x:v>
+        <x:v>99.642</x:v>
       </x:c>
       <x:c r="I24" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
         <x:v>Kovera Labs</x:v>
@@ -10870,13 +12002,13 @@
         <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L24" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M24" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
+        <x:v>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -10884,43 +12016,43 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="14" t="str">
-        <x:v>COA-0020</x:v>
+        <x:v>COA-0033</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E25" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F25" s="14" t="n">
-        <x:v>12.19</x:v>
+        <x:v>33.24</x:v>
       </x:c>
       <x:c r="G25" s="16" t="n">
-        <x:v>0.2189999999999999</x:v>
+        <x:v>0.10800000000000001</x:v>
       </x:c>
       <x:c r="H25" s="18" t="n">
-        <x:v>99.589</x:v>
+        <x:v>99.6</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Janoshik</x:v>
-      </x:c>
-      <x:c r="K25" s="14" t="n">
-        <x:v>46057</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K25" s="14" t="str">
+        <x:v>2026-07-03</x:v>
       </x:c>
       <x:c r="L25" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M25" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -10928,34 +12060,34 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="14" t="str">
-        <x:v>COA-0031</x:v>
+        <x:v>COA-0020</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="D26" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Other</x:v>
       </x:c>
       <x:c r="E26" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="14" t="n">
-        <x:v>33.77</x:v>
+        <x:v>12.19</x:v>
       </x:c>
       <x:c r="G26" s="16" t="n">
-        <x:v>0.12566666666666668</x:v>
+        <x:v>0.2189999999999999</x:v>
       </x:c>
       <x:c r="H26" s="18" t="n">
-        <x:v>99.58</x:v>
+        <x:v>99.589</x:v>
       </x:c>
       <x:c r="I26" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K26" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K26" s="14" t="n">
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L26" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -10964,7 +12096,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -10972,43 +12104,43 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>COA-0040</x:v>
+        <x:v>COA-0031</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E27" s="14" t="n">
-        <x:v>5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F27" s="14" t="n">
-        <x:v>5.13</x:v>
+        <x:v>33.77</x:v>
       </x:c>
       <x:c r="G27" s="16" t="n">
-        <x:v>0.025999999999999978</x:v>
+        <x:v>0.12566666666666668</x:v>
       </x:c>
       <x:c r="H27" s="18" t="n">
-        <x:v>99.57</x:v>
+        <x:v>99.58</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K27" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K27" s="14" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L27" s="14" t="str">
-        <x:v>Green</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M27" s="14" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -11016,43 +12148,43 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" s="14" t="str">
-        <x:v>COA-0026</x:v>
+        <x:v>COA-0040</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>BPC-157</x:v>
       </x:c>
       <x:c r="D28" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E28" s="14" t="n">
-        <x:v>40</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F28" s="14" t="n">
-        <x:v>42.53</x:v>
+        <x:v>5.13</x:v>
       </x:c>
       <x:c r="G28" s="16" t="n">
-        <x:v>0.06325</x:v>
+        <x:v>0.025999999999999978</x:v>
       </x:c>
       <x:c r="H28" s="18" t="n">
-        <x:v>99.569</x:v>
+        <x:v>99.57</x:v>
       </x:c>
       <x:c r="I28" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J28" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
-      </x:c>
-      <x:c r="K28" s="14" t="str">
-        <x:v>2026-06-20</x:v>
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="K28" s="14" t="n">
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L28" s="14" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Green</x:v>
       </x:c>
       <x:c r="M28" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>Blue cap Retatrutide 40mg</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -11060,7 +12192,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>COA-0025</x:v>
+        <x:v>COA-0026</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11069,16 +12201,16 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E29" s="14" t="n">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F29" s="14" t="n">
-        <x:v>33.31</x:v>
+        <x:v>42.53</x:v>
       </x:c>
       <x:c r="G29" s="16" t="n">
-        <x:v>0.1103333333333333</x:v>
+        <x:v>0.06325</x:v>
       </x:c>
       <x:c r="H29" s="18" t="n">
-        <x:v>99.563</x:v>
+        <x:v>99.569</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
         <x:v>Overfilled</x:v>
@@ -11090,13 +12222,13 @@
         <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L29" s="14" t="str">
-        <x:v>Transparent</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M29" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>Transparent cap Retatrutide 30mg</x:v>
+        <x:v>Blue cap Retatrutide 40mg</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -11104,43 +12236,43 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
-        <x:v>COA-0038</x:v>
+        <x:v>COA-0025</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D30" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E30" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F30" s="14" t="n">
-        <x:v>10.09</x:v>
+        <x:v>33.31</x:v>
       </x:c>
       <x:c r="G30" s="16" t="n">
-        <x:v>0.008999999999999985</x:v>
+        <x:v>0.1103333333333333</x:v>
       </x:c>
       <x:c r="H30" s="18" t="n">
-        <x:v>99.52</x:v>
+        <x:v>99.563</x:v>
       </x:c>
       <x:c r="I30" s="14" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J30" s="14" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K30" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K30" s="14" t="str">
+        <x:v>2026-06-20</x:v>
       </x:c>
       <x:c r="L30" s="14" t="str">
-        <x:v>Yellow</x:v>
+        <x:v>Transparent</x:v>
       </x:c>
       <x:c r="M30" s="14" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Transparent cap Retatrutide 30mg</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -11148,43 +12280,43 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="14" t="str">
-        <x:v>COA-0001</x:v>
+        <x:v>COA-0046</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="D31" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
       <x:c r="E31" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="F31" s="14" t="n">
-        <x:v>11.8</x:v>
+        <x:v>488.47</x:v>
       </x:c>
       <x:c r="G31" s="16" t="n">
-        <x:v>0.1800000000000001</x:v>
+        <x:v>-0.023059999999999945</x:v>
       </x:c>
       <x:c r="H31" s="18" t="n">
-        <x:v>99.516</x:v>
+        <x:v>99.549</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K31" s="14" t="n">
-        <x:v>46156</x:v>
+        <x:v>46232</x:v>
       </x:c>
       <x:c r="L31" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Black</x:v>
       </x:c>
       <x:c r="M31" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -11192,39 +12324,43 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="14" t="str">
-        <x:v>COA-0006</x:v>
+        <x:v>COA-0038</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="D32" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E32" s="14"/>
+      <x:c r="E32" s="14" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F32" s="14" t="n">
-        <x:v>22.47</x:v>
-      </x:c>
-      <x:c r="G32" s="16"/>
+        <x:v>10.09</x:v>
+      </x:c>
+      <x:c r="G32" s="16" t="n">
+        <x:v>0.008999999999999985</x:v>
+      </x:c>
       <x:c r="H32" s="18" t="n">
-        <x:v>99.5</x:v>
+        <x:v>99.52</x:v>
       </x:c>
       <x:c r="I32" s="14" t="str">
-        <x:v>Review</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J32" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K32" s="14" t="n">
-        <x:v>46146</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L32" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Yellow</x:v>
       </x:c>
       <x:c r="M32" s="14" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>Labeled quantity unclear from image</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -11232,7 +12368,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="14" t="str">
-        <x:v>COA-0004</x:v>
+        <x:v>COA-0001</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11241,25 +12377,25 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E33" s="14" t="n">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="14" t="n">
-        <x:v>17.93</x:v>
+        <x:v>11.8</x:v>
       </x:c>
       <x:c r="G33" s="16" t="n">
-        <x:v>0.1953333333333333</x:v>
+        <x:v>0.1800000000000001</x:v>
       </x:c>
       <x:c r="H33" s="18" t="n">
-        <x:v>99.491</x:v>
+        <x:v>99.516</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J33" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K33" s="14" t="n">
-        <x:v>46175</x:v>
+        <x:v>46156</x:v>
       </x:c>
       <x:c r="L33" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -11268,7 +12404,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>Heavy metals negative; endotoxin pass</x:v>
+        <x:v>RT10 - common GLP-1 blind test; overfilled</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -11276,7 +12412,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="14" t="str">
-        <x:v>COA-0030</x:v>
+        <x:v>COA-0006</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11284,26 +12420,22 @@
       <x:c r="D34" s="14" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
-      <x:c r="E34" s="14" t="n">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="E34" s="14"/>
       <x:c r="F34" s="14" t="n">
-        <x:v>21.4</x:v>
-      </x:c>
-      <x:c r="G34" s="16" t="n">
-        <x:v>0.06999999999999999</x:v>
-      </x:c>
+        <x:v>22.47</x:v>
+      </x:c>
+      <x:c r="G34" s="16"/>
       <x:c r="H34" s="18" t="n">
-        <x:v>99.49</x:v>
+        <x:v>99.5</x:v>
       </x:c>
       <x:c r="I34" s="14" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>Review</x:v>
       </x:c>
       <x:c r="J34" s="14" t="str">
-        <x:v>Testides</x:v>
-      </x:c>
-      <x:c r="K34" s="14" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>Aminos Analytics</x:v>
+      </x:c>
+      <x:c r="K34" s="14" t="n">
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="L34" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -11312,7 +12444,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Labeled quantity unclear from image</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -11320,7 +12452,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="14" t="str">
-        <x:v>COA-0043</x:v>
+        <x:v>COA-0004</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
         <x:v>Retatrutide</x:v>
@@ -11329,34 +12461,34 @@
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E35" s="14" t="n">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F35" s="14" t="n">
-        <x:v>10.36</x:v>
+        <x:v>17.93</x:v>
       </x:c>
       <x:c r="G35" s="16" t="n">
-        <x:v>0.03599999999999994</x:v>
+        <x:v>0.1953333333333333</x:v>
       </x:c>
       <x:c r="H35" s="18" t="n">
-        <x:v>99.41</x:v>
+        <x:v>99.491</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J35" s="14" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="K35" s="14" t="n">
-        <x:v>46239</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="L35" s="14" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M35" s="14" t="str">
-        <x:v>Copper</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Heavy metals negative; endotoxin pass</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -11364,25 +12496,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>COA-0029</x:v>
+        <x:v>COA-0030</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E36" t="n">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F36" t="n">
-        <x:v>45.03</x:v>
+        <x:v>21.4</x:v>
       </x:c>
       <x:c r="G36" t="n">
-        <x:v>0.12575</x:v>
+        <x:v>0.06999999999999999</x:v>
       </x:c>
       <x:c r="H36" t="n">
-        <x:v>99.39</x:v>
+        <x:v>99.49</x:v>
       </x:c>
       <x:c r="I36" t="str">
         <x:v>Overfilled</x:v>
@@ -11400,7 +12532,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
+        <x:v>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -11408,7 +12540,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>COA-0002</x:v>
+        <x:v>COA-0043</x:v>
       </x:c>
       <x:c r="C37" t="str">
         <x:v>Retatrutide</x:v>
@@ -11420,31 +12552,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" t="n">
-        <x:v>10</x:v>
+        <x:v>10.36</x:v>
       </x:c>
       <x:c r="G37" t="n">
-        <x:v>0</x:v>
+        <x:v>0.03599999999999994</x:v>
       </x:c>
       <x:c r="H37" t="n">
-        <x:v>99.369</x:v>
+        <x:v>99.41</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J37" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K37" t="n">
-        <x:v>46057</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L37" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="M37" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Copper</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>On label</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -11452,43 +12584,43 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>COA-0042</x:v>
+        <x:v>COA-0029</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E38" t="n">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F38" t="n">
-        <x:v>5.17</x:v>
+        <x:v>45.03</x:v>
       </x:c>
       <x:c r="G38" t="n">
-        <x:v>0.03399999999999999</x:v>
+        <x:v>0.12575</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>99.34</x:v>
+        <x:v>99.39</x:v>
       </x:c>
       <x:c r="I38" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>SteriGenix</x:v>
-      </x:c>
-      <x:c r="K38" t="n">
-        <x:v>46239</x:v>
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="K38" t="str">
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="L38" t="str">
-        <x:v>White</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M38" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -11496,43 +12628,43 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>COA-0039</x:v>
+        <x:v>COA-0002</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="D39" t="str">
         <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E39" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F39" t="n">
-        <x:v>5.07</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G39" t="n">
-        <x:v>0.014000000000000058</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H39" t="n">
-        <x:v>99.32</x:v>
+        <x:v>99.369</x:v>
       </x:c>
       <x:c r="I39" t="str">
         <x:v>On label</x:v>
       </x:c>
       <x:c r="J39" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K39" t="n">
-        <x:v>46239</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L39" t="str">
-        <x:v>Blue</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="M39" t="str">
-        <x:v>Silver</x:v>
+        <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>On label</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11540,25 +12672,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>COA-0037</x:v>
+        <x:v>COA-0042</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>BPC-157 / TB-500 Blend</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
       <x:c r="E40" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F40" t="n">
-        <x:v>10.55</x:v>
+        <x:v>5.17</x:v>
       </x:c>
       <x:c r="G40" t="n">
-        <x:v>0.05500000000000007</x:v>
+        <x:v>0.03399999999999999</x:v>
       </x:c>
       <x:c r="H40" t="n">
-        <x:v>99.13</x:v>
+        <x:v>99.34</x:v>
       </x:c>
       <x:c r="I40" t="str">
         <x:v>Overfilled</x:v>
@@ -11570,13 +12702,13 @@
         <x:v>46239</x:v>
       </x:c>
       <x:c r="L40" t="str">
-        <x:v>Red</x:v>
+        <x:v>White</x:v>
       </x:c>
       <x:c r="M40" t="str">
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -11584,43 +12716,43 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>COA-0016</x:v>
+        <x:v>COA-0039</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E41" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F41" t="n">
-        <x:v>11.38</x:v>
+        <x:v>5.07</x:v>
       </x:c>
       <x:c r="G41" t="n">
-        <x:v>0.1380000000000001</x:v>
+        <x:v>0.014000000000000058</x:v>
       </x:c>
       <x:c r="H41" t="n">
-        <x:v>99.085</x:v>
+        <x:v>99.32</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>On label</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K41" t="n">
-        <x:v>46155</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Blue</x:v>
       </x:c>
       <x:c r="M41" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>TB-500 / TB4</x:v>
+        <x:v>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -11628,43 +12760,43 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>COA-0014</x:v>
+        <x:v>COA-0037</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
       <x:c r="E42" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" t="n">
-        <x:v>11.17</x:v>
+        <x:v>10.55</x:v>
       </x:c>
       <x:c r="G42" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.05500000000000007</x:v>
       </x:c>
       <x:c r="H42" t="n">
-        <x:v>99.055</x:v>
+        <x:v>99.13</x:v>
       </x:c>
       <x:c r="I42" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J42" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="K42" t="n">
-        <x:v>46155</x:v>
+        <x:v>46239</x:v>
       </x:c>
       <x:c r="L42" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Red</x:v>
       </x:c>
       <x:c r="M42" t="str">
-        <x:v>Not Listed</x:v>
+        <x:v>Silver</x:v>
       </x:c>
       <x:c r="N42" t="str">
-        <x:v>MS10 / MOTS-C</x:v>
+        <x:v>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -11672,28 +12804,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>COA-0011</x:v>
+        <x:v>COA-0016</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>TB-500</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
       <x:c r="E43" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" t="n">
-        <x:v>10.47</x:v>
+        <x:v>11.38</x:v>
       </x:c>
       <x:c r="G43" t="n">
-        <x:v>0.04700000000000006</x:v>
+        <x:v>0.1380000000000001</x:v>
       </x:c>
       <x:c r="H43" t="n">
-        <x:v>99.04</x:v>
+        <x:v>99.085</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>On label</x:v>
+        <x:v>Overfilled</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Janoshik</x:v>
@@ -11708,7 +12840,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N43" t="str">
-        <x:v>Overfilled</x:v>
+        <x:v>TB-500 / TB4</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -11716,24 +12848,26 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>COA-0017</x:v>
+        <x:v>COA-0014</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>BPC-157</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
       <x:c r="E44" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F44" t="n">
-        <x:v>5.54</x:v>
+        <x:v>11.17</x:v>
       </x:c>
       <x:c r="G44" t="n">
-        <x:v>0.108</x:v>
-      </x:c>
-      <x:c r="H44"/>
+        <x:v>0.117</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>99.055</x:v>
+      </x:c>
       <x:c r="I44" t="str">
         <x:v>Overfilled</x:v>
       </x:c>
@@ -11741,7 +12875,7 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K44" t="n">
-        <x:v>46057</x:v>
+        <x:v>46155</x:v>
       </x:c>
       <x:c r="L44" t="str">
         <x:v>Not Listed</x:v>
@@ -11750,7 +12884,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="N44" t="str">
-        <x:v>Blend report BPC5+TB5</x:v>
+        <x:v>MS10 / MOTS-C</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -11758,24 +12892,26 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>COA-0018</x:v>
+        <x:v>COA-0011</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
       <x:c r="E45" t="n">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F45" t="n">
-        <x:v>5.43</x:v>
+        <x:v>10.47</x:v>
       </x:c>
       <x:c r="G45" t="n">
-        <x:v>0.08599999999999994</x:v>
-      </x:c>
-      <x:c r="H45"/>
+        <x:v>0.04700000000000006</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>99.04</x:v>
+      </x:c>
       <x:c r="I45" t="str">
         <x:v>On label</x:v>
       </x:c>
@@ -11783,15 +12919,99 @@
         <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="K45" t="n">
+        <x:v>46155</x:v>
+      </x:c>
+      <x:c r="L45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M45" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N45" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>COA-0017</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>BPC-157</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>5.54</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.108</x:v>
+      </x:c>
+      <x:c r="H46"/>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
         <x:v>46057</x:v>
       </x:c>
-      <x:c r="L45" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="M45" t="str">
-        <x:v>Not Listed</x:v>
-      </x:c>
-      <x:c r="N45" t="str">
+      <x:c r="L46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Blend report BPC5+TB5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>COA-0018</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Healing / Recovery</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>5.43</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>0.08599999999999994</x:v>
+      </x:c>
+      <x:c r="H47"/>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Janoshik</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L47" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
         <x:v>Blend report BPC5+TB5</x:v>
       </x:c>
     </x:row>
@@ -13763,7 +14983,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13831,7 +15051,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13899,7 +15119,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Pass</x:v>
@@ -13967,7 +15187,7 @@
         <x:v>BATCH-01</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Pass</x:v>
@@ -14239,7 +15459,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Pass</x:v>
@@ -14375,7 +15595,7 @@
         <x:v>BB260725A</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Pass</x:v>
@@ -14443,7 +15663,7 @@
         <x:v>TR260725A</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Pass</x:v>
@@ -14511,7 +15731,7 @@
         <x:v>SM260725A</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Pass</x:v>
@@ -14579,7 +15799,7 @@
         <x:v>BC260725A</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Pass</x:v>
@@ -14647,7 +15867,7 @@
         <x:v>CU260725A</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Pass</x:v>
@@ -14715,7 +15935,7 @@
         <x:v>IP260725A</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>Pass</x:v>
@@ -14783,7 +16003,7 @@
         <x:v>RT260725A</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Pass</x:v>
@@ -14851,7 +16071,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Pass</x:v>
@@ -14870,6 +16090,142 @@
       </x:c>
       <x:c r="V45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>Confirmed</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Duplicates removed by same lab/report/date/product</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14903,16 +16259,16 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>Aminos Analytics</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Retatrutide, Tirzepatide 30, Cagrilintide, AOD-9604, MOTS-C, TB-500, BPC-157, SS-31, KPV, CJC-1295 No DAC</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>Janoshik task number + verify key</x:v>
+        <x:v>Aminos certificate</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Task/report numbers preserved in COA Database</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -14920,55 +16276,111 @@
         <x:v>BT Labs</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
-        <x:v>Tirzepatide 20, Tirzepatide 40, Tirzepatide 60</x:v>
+        <x:v>Tirzepatide</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
         <x:v>BT Labs report number</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>BT Labs reports use IF-824-QSA-TR006 report IDs</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Freedom Diagnostics</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>Retatrutide 5, Retatrutide 10 / Trivial-3R, Retatrutide 15</x:v>
+        <x:v>GHK-Cu, KLOW 80mg, Retatrutide</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>Kovera certificate</x:v>
+        <x:v>Freedom Diagnostics accession/search code + COA PDF</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>Heavy metals/endotoxin screening shown on certificates</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="14" t="str">
-        <x:v>Aminos Analytics</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>Aminos certificate</x:v>
+        <x:v>ILS Laboratories certificate / HPLC report</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>Labeled quantity unclear in image; marked N/A/unclear</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="14" t="str">
-        <x:v>Freedom Diagnostics</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Retatrutide 20mg, KLOW 80mg</x:v>
+        <x:v>AOD-9604, BPC-157, CJC-1295 No DAC, Cagrilintide, KPV, MOTS-C, Retatrutide, SS-31, TB-500, Tirzepatide</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
-        <x:v>Freedom Diagnostics accession/search code + COA PDF</x:v>
+        <x:v>Janoshik task number + verify key</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>Accession and search code preserved; vial closure colors documented from COA image.</x:v>
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>NAD+, Retatrutide, Semaglutide, Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Kovera certificate</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>SteriGenix</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>ADAMAX, BPC-157, BPC-157 / TB-500 Blend, GHK-Cu, Ipamorelin, Retatrutide, Semaglutide, Tirzepatide</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>SteriGenix report/task number + verification key + COA PDF</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>Testides</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>BPC/TB Blend, MOTS-C, Retatrutide</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Testides report image / certificate</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>Partner laboratory report PDF</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Records preserved in COA Database and Certificates tabs.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16769,7 +18181,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="P29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q29" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16831,7 +18243,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="P30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q30" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16893,7 +18305,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="P31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q31" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -16955,7 +18367,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="P32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="Q32" s="14" t="str">
         <x:v>Not Listed</x:v>
@@ -17203,7 +18615,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="P36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="Q36" s="14" t="str">
         <x:v>Clear/Transparent</x:v>
@@ -17327,7 +18739,7 @@
         <x:v>SGX-VP-2026-0728-G37</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q38" t="str">
         <x:v>Red</x:v>
@@ -17389,7 +18801,7 @@
         <x:v>SGX-VP-2026-0728-K72</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q39" t="str">
         <x:v>Yellow</x:v>
@@ -17451,7 +18863,7 @@
         <x:v>SGX-VP-2026-0728-U17</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q40" t="str">
         <x:v>Blue</x:v>
@@ -17513,7 +18925,7 @@
         <x:v>SGX-VP-2026-0728-Z53</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q41" t="str">
         <x:v>Green</x:v>
@@ -17575,7 +18987,7 @@
         <x:v>SGX-VP-2026-0728-K16</x:v>
       </x:c>
       <x:c r="P42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q42" t="str">
         <x:v>Blue</x:v>
@@ -17637,7 +19049,7 @@
         <x:v>SGX-VP-2026-0728-U21</x:v>
       </x:c>
       <x:c r="P43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q43" t="str">
         <x:v>White</x:v>
@@ -17699,7 +19111,7 @@
         <x:v>SGX-VP-2026-0728-G60</x:v>
       </x:c>
       <x:c r="P44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="Q44" t="str">
         <x:v>Clear</x:v>
@@ -17761,7 +19173,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="P45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="Q45" t="str">
         <x:v>Not Listed</x:v>
@@ -17774,6 +19186,130 @@
       </x:c>
       <x:c r="T45" t="str">
         <x:v>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="M46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="I47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="J47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="M47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19632,7 +21168,7 @@
         <x:v>da424443</x:v>
       </x:c>
       <x:c r="G29" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-BPCTB-10-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/bpc-tb-blend/PT-BPCTB-10-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H29" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19697,7 +21233,7 @@
         <x:v>96ea8238</x:v>
       </x:c>
       <x:c r="G30" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-MOTS-40-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/mots-c/PT-MOTS-40-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H30" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19762,7 +21298,7 @@
         <x:v>5c1aa528</x:v>
       </x:c>
       <x:c r="G31" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-20-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-20-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H31" s="14" t="str">
         <x:v>Yes</x:v>
@@ -19827,7 +21363,7 @@
         <x:v>a8c10db6</x:v>
       </x:c>
       <x:c r="G32" s="14" t="str">
-        <x:v>Local PDF: assets/coa/PT-RETA-30-062226-01.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/retatrutide/PT-RETA-30-062226-01.pdf</x:v>
       </x:c>
       <x:c r="H32" s="14" t="str">
         <x:v>Yes</x:v>
@@ -20087,7 +21623,7 @@
         <x:v>Redacted</x:v>
       </x:c>
       <x:c r="G36" s="14" t="str">
-        <x:v>Local image: assets/coa/GHK-CU50MG%207-19-26.jpg</x:v>
+        <x:v>Local image: assets/coa/images/freedom-diagnostics/ghk-cu/GHK-CU50MG-2026-06-29-Freedom.jpg</x:v>
       </x:c>
       <x:c r="H36" s="14" t="str">
         <x:v>Yes</x:v>
@@ -20217,7 +21753,7 @@
         <x:v>SGX-VP-2026-0728-G37</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-237183%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157-tb-500-blend/COA-RPT-2026-237183-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>Yes</x:v>
@@ -20282,7 +21818,7 @@
         <x:v>SGX-VP-2026-0728-K72</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-442015%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/tirzepatide/COA-RPT-2026-442015-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>Yes</x:v>
@@ -20347,7 +21883,7 @@
         <x:v>SGX-VP-2026-0728-U17</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-538821%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/semaglutide/COA-RPT-2026-538821-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>Yes</x:v>
@@ -20412,7 +21948,7 @@
         <x:v>SGX-VP-2026-0728-Z53</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-654610%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/bpc-157/COA-RPT-2026-654610-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>Yes</x:v>
@@ -20477,7 +22013,7 @@
         <x:v>SGX-VP-2026-0728-K16</x:v>
       </x:c>
       <x:c r="G42" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-697297%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-697297-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H42" t="str">
         <x:v>Yes</x:v>
@@ -20542,7 +22078,7 @@
         <x:v>SGX-VP-2026-0728-U21</x:v>
       </x:c>
       <x:c r="G43" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-822844%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/ipamorelin/COA-RPT-2026-822844-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H43" t="str">
         <x:v>Yes</x:v>
@@ -20607,7 +22143,7 @@
         <x:v>SGX-VP-2026-0728-G60</x:v>
       </x:c>
       <x:c r="G44" t="str">
-        <x:v>Local PDF: assets/coa/COA%20RPT-2026-932680%20-%20SteriGenix.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/sterigenix/retatrutide/COA-RPT-2026-932680-SteriGenix.pdf</x:v>
       </x:c>
       <x:c r="H44" t="str">
         <x:v>Yes</x:v>
@@ -20672,7 +22208,7 @@
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="G45" t="str">
-        <x:v>Local PDF: assets/coa/Elor5-20260731S0925_report.pdf</x:v>
+        <x:v>Local PDF: assets/coa/documents/tianjin-qiangxin/eloralintide/Elor5-20260731S0925-report.pdf</x:v>
       </x:c>
       <x:c r="H45" t="str">
         <x:v>Yes</x:v>
@@ -20715,6 +22251,136 @@
       </x:c>
       <x:c r="U45" t="str">
         <x:v>Crimp/cap color not listed in the testing record.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>COA-0045</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>CJC-1295</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>GHRH analog</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>ILS Laboratories</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F46" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>Local PDF: assets/coa/documents/ils-laboratories/cjc-1295/CJC-1295-10mg-2026-07-31-ILS.pdf</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>10.52</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>0.5199999999999996</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>0.051999999999999956</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>99.72</x:v>
+      </x:c>
+      <x:c r="N46" t="str">
+        <x:v>Overfilled</x:v>
+      </x:c>
+      <x:c r="O46" t="str">
+        <x:v>CND10-2606</x:v>
+      </x:c>
+      <x:c r="P46" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="Q46" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</x:v>
+      </x:c>
+      <x:c r="S46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:v>Not Listed</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>Crimp/cap color not listed or visible in the supplied COA image.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>COA-0046</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>NAD+</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>Metabolic / Cellular Energy</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>Kovera Labs</x:v>
+      </x:c>
+      <x:c r="E47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="F47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="G47" t="str">
+        <x:v>Local PDF: assets/coa/documents/kovera-labs/nad-plus/NAD-500mg-2026-07-29-Kovera.pdf</x:v>
+      </x:c>
+      <x:c r="H47" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>488.47</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>-11.529999999999973</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>-0.023059999999999945</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>99.549</x:v>
+      </x:c>
+      <x:c r="N47" t="str">
+        <x:v>On label</x:v>
+      </x:c>
+      <x:c r="O47" t="str">
+        <x:v>Redacted</x:v>
+      </x:c>
+      <x:c r="P47" t="n">
+        <x:v>46232</x:v>
+      </x:c>
+      <x:c r="Q47" t="str">
+        <x:v>Pass</x:v>
+      </x:c>
+      <x:c r="R47" t="str">
+        <x:v>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</x:v>
+      </x:c>
+      <x:c r="S47" t="str">
+        <x:v>Silver</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:v>Black</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>Black flip-off cap with silver aluminum crimp, as listed in the COA.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -20811,7 +22477,7 @@
         <x:v>Silver</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>GLP-1 / Weight</x:v>
+        <x:v>GHRH analog</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -20819,7 +22485,7 @@
         <x:v>BPC-157 / TB-500 Blend</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Janoshik</x:v>
+        <x:v>ILS Laboratories</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>Underfilled</x:v>
@@ -20829,7 +22495,7 @@
       </x:c>
       <x:c r="E5" s="14"/>
       <x:c r="F5" s="14" t="str">
-        <x:v>Growth Hormone Support</x:v>
+        <x:v>GLP-1 / Weight</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -20837,7 +22503,7 @@
         <x:v>BPC/TB Blend</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>Kovera Labs</x:v>
+        <x:v>Janoshik</x:v>
       </x:c>
       <x:c r="C6" s="14"/>
       <x:c r="D6" s="14" t="str">
@@ -20845,15 +22511,15 @@
       </x:c>
       <x:c r="E6" s="14"/>
       <x:c r="F6" s="14" t="str">
-        <x:v>Healing / Recovery</x:v>
+        <x:v>Growth Hormone Support</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="14" t="str">
-        <x:v>CJC-1295 No DAC</x:v>
+        <x:v>CJC-1295</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>SteriGenix</x:v>
+        <x:v>Kovera Labs</x:v>
       </x:c>
       <x:c r="C7" s="14"/>
       <x:c r="D7" s="14" t="str">
@@ -20861,15 +22527,15 @@
       </x:c>
       <x:c r="E7" s="14"/>
       <x:c r="F7" s="14" t="str">
-        <x:v>Healing / Recovery Blend</x:v>
+        <x:v>Healing / Recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="14" t="str">
-        <x:v>Cagrilintide</x:v>
+        <x:v>CJC-1295 No DAC</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>Testides</x:v>
+        <x:v>SteriGenix</x:v>
       </x:c>
       <x:c r="C8" s="14"/>
       <x:c r="D8" s="14" t="str">
@@ -20877,15 +22543,15 @@
       </x:c>
       <x:c r="E8" s="14"/>
       <x:c r="F8" s="14" t="str">
-        <x:v>Metabolic / Fat Loss</x:v>
+        <x:v>Healing / Recovery Blend</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="14" t="str">
-        <x:v>Eloralintide</x:v>
+        <x:v>Cagrilintide</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+        <x:v>Testides</x:v>
       </x:c>
       <x:c r="C9" s="14"/>
       <x:c r="D9" s="14" t="str">
@@ -20893,26 +22559,28 @@
       </x:c>
       <x:c r="E9" s="14"/>
       <x:c r="F9" s="14" t="str">
-        <x:v>Metabolic / Mito</x:v>
+        <x:v>Metabolic / Cellular Energy</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="14" t="str">
-        <x:v>GHK-Cu</x:v>
-      </x:c>
-      <x:c r="B10" s="14"/>
+        <x:v>Eloralintide</x:v>
+      </x:c>
+      <x:c r="B10" s="14" t="str">
+        <x:v>Tianjin Qiangxin (third-party partner lab)</x:v>
+      </x:c>
       <x:c r="C10" s="14"/>
       <x:c r="D10" s="14" t="str">
         <x:v>Not Listed</x:v>
       </x:c>
       <x:c r="E10" s="14"/>
       <x:c r="F10" s="14" t="str">
-        <x:v>Other</x:v>
+        <x:v>Metabolic / Fat Loss</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="14" t="str">
-        <x:v>Ipamorelin</x:v>
+        <x:v>GHK-Cu</x:v>
       </x:c>
       <x:c r="B11" s="14"/>
       <x:c r="C11" s="14"/>
@@ -20921,12 +22589,12 @@
       </x:c>
       <x:c r="E11" s="14"/>
       <x:c r="F11" s="14" t="str">
-        <x:v>Regenerative / Skin</x:v>
+        <x:v>Metabolic / Mito</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="14" t="str">
-        <x:v>KLOW 80mg</x:v>
+        <x:v>Ipamorelin</x:v>
       </x:c>
       <x:c r="B12" s="14"/>
       <x:c r="C12" s="14"/>
@@ -20935,12 +22603,12 @@
       </x:c>
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14" t="str">
-        <x:v>Research Peptide</x:v>
+        <x:v>Other</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="14" t="str">
-        <x:v>KPV</x:v>
+        <x:v>KLOW 80mg</x:v>
       </x:c>
       <x:c r="B13" s="14"/>
       <x:c r="C13" s="14"/>
@@ -20948,11 +22616,13 @@
         <x:v>Royal Blue</x:v>
       </x:c>
       <x:c r="E13" s="14"/>
-      <x:c r="F13" s="14"/>
+      <x:c r="F13" s="14" t="str">
+        <x:v>Regenerative / Skin</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="14" t="str">
-        <x:v>MOTS-C</x:v>
+        <x:v>KPV</x:v>
       </x:c>
       <x:c r="B14" s="14"/>
       <x:c r="C14" s="14"/>
@@ -20960,11 +22630,13 @@
         <x:v>Transparent</x:v>
       </x:c>
       <x:c r="E14" s="14"/>
-      <x:c r="F14" s="14"/>
+      <x:c r="F14" s="14" t="str">
+        <x:v>Research Peptide</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="14" t="str">
-        <x:v>Retatrutide</x:v>
+        <x:v>MOTS-C</x:v>
       </x:c>
       <x:c r="B15" s="14"/>
       <x:c r="C15" s="14"/>
@@ -20976,7 +22648,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="str">
-        <x:v>SS-31</x:v>
+        <x:v>NAD+</x:v>
       </x:c>
       <x:c r="B16"/>
       <x:c r="C16"/>
@@ -20988,7 +22660,7 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="str">
-        <x:v>Semaglutide</x:v>
+        <x:v>Retatrutide</x:v>
       </x:c>
       <x:c r="B17"/>
       <x:c r="C17"/>
@@ -20998,7 +22670,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="str">
-        <x:v>TB-500</x:v>
+        <x:v>SS-31</x:v>
       </x:c>
       <x:c r="B18"/>
       <x:c r="C18"/>
@@ -21008,13 +22680,33 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="str">
-        <x:v>Tirzepatide</x:v>
+        <x:v>Semaglutide</x:v>
       </x:c>
       <x:c r="B19"/>
       <x:c r="C19"/>
       <x:c r="D19"/>
       <x:c r="E19"/>
       <x:c r="F19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>TB-500</x:v>
+      </x:c>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Tirzepatide</x:v>
+      </x:c>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -37,6 +37,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0049" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0050" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +478,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -491,11 +493,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
+          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
         </is>
       </c>
     </row>
@@ -506,7 +508,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.59999999999999</v>
+        <v>99.59399999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -571,7 +573,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -1235,7 +1236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1269,7 +1270,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1284,11 +1285,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, Cagrilintide, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
+          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1300,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1314,7 +1315,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1344,7 +1345,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,7 +1360,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99.614</v>
+        <v>99.59399999999999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1390,7 +1391,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5400,6 +5401,609 @@
       <c r="S59" t="inlineStr">
         <is>
           <t>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COA-0047</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" t="n">
+        <v>63.37</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.369999999999997</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.05616666666666662</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COA-0048</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SS-31</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Metabolic / Mito</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>50</v>
+      </c>
+      <c r="E61" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.520000000000003</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.03040000000000006</v>
+      </c>
+      <c r="H61" t="n">
+        <v>99.31999999999999</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Purple flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>COA-0049</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5-Amino-1MQ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Metabolic / Research</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>50</v>
+      </c>
+      <c r="E62" t="n">
+        <v>51.88</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.880000000000003</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.03760000000000005</v>
+      </c>
+      <c r="H62" t="n">
+        <v>99.369</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COA-0050</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cagrilintide</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Amylin / Weight</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="H63" t="n">
+        <v>99.849</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>46242</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Purple flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>COA-0051</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>DSIP</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sleep / Research</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.01600000000000001</v>
+      </c>
+      <c r="H64" t="n">
+        <v>99.464</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H65" t="n">
+        <v>99.446</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>46242</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>100</v>
+      </c>
+      <c r="E66" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H66" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>46224</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
         </is>
       </c>
     </row>
@@ -9843,7 +10447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14826,7 +15430,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Local image: assets/coa/images/kovera-labs/5-amino-1mq/5-Amino-1MQ-50mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/5-amino-1mq/5-Amino-1MQ-50mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -14880,16 +15484,16 @@
         <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>10.16</v>
+        <v>10.38</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="H51" t="n">
-        <v>99.639</v>
+        <v>99.849</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -14906,10 +15510,8 @@
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="L51" t="n">
+        <v>46242</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14923,12 +15525,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Redacted</t>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Local image: assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-08-08-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -14938,12 +15540,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Unique supplied Kovera certificate image.</t>
+          <t>Replaces earlier transcription for the same supplied certificate image</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -15061,6 +15663,206 @@
       <c r="V52" t="inlineStr">
         <is>
           <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H53" t="n">
+        <v>99.446</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cjc-1295-no-dac-ipamorelin/CJC-1295-No-DAC-Ipamorelin-10mg-2026-08-08-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Unique product/batch/date record</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>46224</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-07-21-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Unique strength/accession/date record</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
         </is>
       </c>
     </row>
@@ -17163,7 +17965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17193,7 +17995,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Compound</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -17229,19 +18031,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Certified</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46242</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report #</t>
+          <t>Report/Task #</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -17253,7 +18053,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Batch/Lot</t>
+          <t>Verification Key</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -17265,114 +18065,126 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Labeled Qty (mg)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>10</v>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Actual Content (mg)</t>
+          <t>Labeled Qty (mg)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10.16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Purity %</t>
+          <t>Actual Content (mg)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99.639</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>On label</t>
-        </is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99.849</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Identity</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Confirmed: Cagrilintide (LC-MS)</t>
+          <t>On label</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Endotoxin Safety Screen</t>
+          <t>Cap Color</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Purple</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Heavy Metals</t>
+          <t>Crimp Color</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arsenic, Cadmium, Lead, Mercury: Negative</t>
+          <t>Silver</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cap Color</t>
+          <t>Closure Notes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Purple flip-off cap with silver aluminum crimp, as listed in the COA.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Crimp Color</t>
+          <t>Pass/Fail</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-07-29-Kovera.jpg</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-08-08-Kovera.jpg</t>
         </is>
       </c>
     </row>
@@ -17387,7 +18199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17832,57 +18644,57 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COA-0013</t>
+          <t>COA-0050</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Cagrilintide</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Amylin / Weight</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>10.58</v>
+        <v>10.38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05800000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="H8" t="n">
-        <v>99.84699999999999</v>
+        <v>99.849</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>46057</v>
+        <v>46242</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10 mg label</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
     </row>
@@ -17892,30 +18704,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COA-0010</t>
+          <t>COA-0013</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>32.5</v>
+        <v>10.58</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.05800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>99.84</v>
+        <v>99.84699999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -17928,7 +18740,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -17942,7 +18754,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30 mg label</t>
+          <t>10 mg label</t>
         </is>
       </c>
     </row>
@@ -17952,12 +18764,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COA-0022</t>
+          <t>COA-0010</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -17969,13 +18781,13 @@
         <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>34.77</v>
+        <v>32.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1590000000000001</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>99.825</v>
+        <v>99.84</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -17988,7 +18800,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>46156</v>
+        <v>46059</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -18002,7 +18814,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</t>
+          <t>30 mg label</t>
         </is>
       </c>
     </row>
@@ -18012,30 +18824,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COA-0036</t>
+          <t>COA-0022</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KLOW 80mg</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Healing / Recovery Blend</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>96.45999999999999</v>
+        <v>34.77</v>
       </c>
       <c r="G11" t="n">
-        <v>0.20575</v>
+        <v>0.1590000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>99.81999999999999</v>
+        <v>99.825</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -18044,27 +18856,25 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>46156</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</t>
+          <t>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</t>
         </is>
       </c>
     </row>
@@ -18074,57 +18884,59 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COA-0015</t>
+          <t>COA-0036</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>KLOW 80mg</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Healing / Recovery Blend</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>38.96</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.02599999999999998</v>
+        <v>0.20575</v>
       </c>
       <c r="H12" t="n">
-        <v>99.813</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>46057</v>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>40 mg label</t>
+          <t>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</t>
         </is>
       </c>
     </row>
@@ -18134,45 +18946,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COA-0028</t>
+          <t>COA-0015</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BPC/TB Blend</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F13" t="n">
-        <v>11.85</v>
+        <v>38.96</v>
       </c>
       <c r="G13" t="n">
-        <v>0.185</v>
+        <v>-0.02599999999999998</v>
       </c>
       <c r="H13" t="n">
-        <v>99.81</v>
+        <v>99.813</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Testides</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>46057</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -18186,7 +18996,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>40 mg label</t>
         </is>
       </c>
     </row>
@@ -18196,30 +19006,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COA-0009</t>
+          <t>COA-0028</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>BPC/TB Blend</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Healing / Recovery</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>65.09999999999999</v>
+        <v>11.85</v>
       </c>
       <c r="G14" t="n">
-        <v>0.08499999999999991</v>
+        <v>0.185</v>
       </c>
       <c r="H14" t="n">
-        <v>99.8</v>
+        <v>99.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -18228,15 +19038,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>BT Labs</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>46133</v>
+          <t>Testides</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -18246,7 +19058,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>60 mg label; 108.5% potency</t>
+          <t>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -18256,30 +19068,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COA-0041</t>
+          <t>COA-0009</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GHK-Cu</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cosmetic / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
-        <v>51.34</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02680000000000007</v>
+        <v>0.08499999999999991</v>
       </c>
       <c r="H15" t="n">
-        <v>99.78</v>
+        <v>99.8</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -18288,25 +19100,25 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
+          <t>BT Labs</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>46239</v>
+        <v>46133</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>60 mg label; 108.5% potency</t>
         </is>
       </c>
     </row>
@@ -18316,7 +19128,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COA-0035</t>
+          <t>COA-0041</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -18326,39 +19138,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Regenerative / Skin</t>
+          <t>Cosmetic / Recovery</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>50.75</v>
+        <v>51.34</v>
       </c>
       <c r="G16" t="n">
-        <v>0.015</v>
+        <v>0.02680000000000007</v>
       </c>
       <c r="H16" t="n">
-        <v>99.77</v>
+        <v>99.78</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>46239</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Clear/Transparent</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -18368,7 +19178,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</t>
+          <t>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -18378,30 +19188,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COA-0034</t>
+          <t>COA-0035</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Regenerative / Skin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
-        <v>15.59</v>
+        <v>50.75</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03933333333333333</v>
+        <v>0.015</v>
       </c>
       <c r="H17" t="n">
-        <v>99.747</v>
+        <v>99.77</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -18410,17 +19220,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>Freedom Diagnostics</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Clear/Transparent</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -18430,7 +19240,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
+          <t>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</t>
         </is>
       </c>
     </row>
@@ -18440,7 +19250,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COA-0023</t>
+          <t>COA-0034</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -18457,40 +19267,42 @@
         <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>16.18</v>
+        <v>15.59</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07866666666666665</v>
+        <v>0.03933333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>99.73099999999999</v>
+        <v>99.747</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>46156</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</t>
+          <t>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
         </is>
       </c>
     </row>
@@ -18500,30 +19312,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COA-0045</t>
+          <t>COA-0023</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CJC-1295</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GHRH analog</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>10.52</v>
+        <v>16.18</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05199999999999996</v>
+        <v>0.07866666666666665</v>
       </c>
       <c r="H19" t="n">
-        <v>99.72</v>
+        <v>99.73099999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -18532,11 +19344,11 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ILS Laboratories</t>
+          <t>Janoshik</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>46234</v>
+        <v>46156</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -18550,7 +19362,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</t>
+          <t>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</t>
         </is>
       </c>
     </row>
@@ -18560,30 +19372,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COA-0007</t>
+          <t>COA-0045</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>CJC-1295</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>GHRH analog</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>10.52</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3</v>
+        <v>0.05199999999999996</v>
       </c>
       <c r="H20" t="n">
-        <v>99.7</v>
+        <v>99.72</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -18592,15 +19404,15 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>BT Labs</t>
+          <t>ILS Laboratories</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>46133</v>
+        <v>46234</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Royal Blue</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -18610,7 +19422,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>20 mg label; 130.1% potency</t>
+          <t>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -18620,7 +19432,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COA-0008</t>
+          <t>COA-0007</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -18634,13 +19446,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>46.6</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.165</v>
+        <v>0.3</v>
       </c>
       <c r="H21" t="n">
         <v>99.7</v>
@@ -18656,11 +19468,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>46106</v>
+        <v>46133</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Royal Blue</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -18670,7 +19482,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>40 mg label; 116.4% potency</t>
+          <t>20 mg label; 130.1% potency</t>
         </is>
       </c>
     </row>
@@ -18680,57 +19492,57 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COA-0044</t>
+          <t>COA-0008</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eloralintide</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Amylin / Weight</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>4.63</v>
+        <v>46.6</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07400000000000002</v>
+        <v>0.165</v>
       </c>
       <c r="H22" t="n">
-        <v>99.67</v>
+        <v>99.7</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Underfilled</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Tianjin Qiangxin (third-party partner lab)</t>
+          <t>BT Labs</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>46234</v>
+        <v>46106</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>Not Listed</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</t>
+          <t>40 mg label; 116.4% potency</t>
         </is>
       </c>
     </row>
@@ -18740,43 +19552,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COA-0003</t>
+          <t>COA-0044</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>Eloralintide</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Amylin / Weight</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>6.63</v>
+        <v>4.63</v>
       </c>
       <c r="G23" t="n">
-        <v>0.326</v>
+        <v>-0.07400000000000002</v>
       </c>
       <c r="H23" t="n">
-        <v>99.654</v>
+        <v>99.67</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>Underfilled</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>Tianjin Qiangxin (third-party partner lab)</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>46174</v>
+        <v>46234</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -18790,7 +19602,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Heavy metals negative; endotoxin pass</t>
+          <t>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</t>
         </is>
       </c>
     </row>
@@ -18800,12 +19612,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COA-0032</t>
+          <t>COA-0003</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18814,20 +19626,20 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>15.53</v>
+        <v>6.63</v>
       </c>
       <c r="G24" t="n">
-        <v>0.03533333333333333</v>
+        <v>0.326</v>
       </c>
       <c r="H24" t="n">
-        <v>99.642</v>
+        <v>99.654</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -18835,24 +19647,22 @@
           <t>Kovera Labs</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
+      <c r="K24" t="n">
+        <v>46174</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</t>
+          <t>Heavy metals negative; endotoxin pass</t>
         </is>
       </c>
     </row>
@@ -18862,30 +19672,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COA-0050</t>
+          <t>COA-0032</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cagrilintide</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Amylin / Weight</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F25" t="n">
-        <v>10.16</v>
+        <v>15.53</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.03533333333333333</v>
       </c>
       <c r="H25" t="n">
-        <v>99.639</v>
+        <v>99.642</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -18899,12 +19709,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -18914,7 +19724,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</t>
         </is>
       </c>
     </row>
@@ -19772,57 +20582,57 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COA-0043</t>
+          <t>COA-0052</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>GHRH / GH Secretagogue Blend</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>10.36</v>
+        <v>10.42</v>
       </c>
       <c r="G40" t="n">
-        <v>0.03599999999999994</v>
+        <v>0.042</v>
       </c>
       <c r="H40" t="n">
-        <v>99.41</v>
+        <v>99.446</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
         </is>
       </c>
     </row>
@@ -19832,30 +20642,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COA-0029</t>
+          <t>COA-0043</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>45.03</v>
+        <v>10.36</v>
       </c>
       <c r="G41" t="n">
-        <v>0.12575</v>
+        <v>0.03599999999999994</v>
       </c>
       <c r="H41" t="n">
-        <v>99.39</v>
+        <v>99.41</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -19864,27 +20674,25 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Testides</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>46239</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -19894,43 +20702,45 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COA-0002</t>
+          <t>COA-0029</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>45.03</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.12575</v>
       </c>
       <c r="H42" t="n">
-        <v>99.369</v>
+        <v>99.39</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>46057</v>
+          <t>Testides</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -19944,7 +20754,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -19954,27 +20764,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COA-0049</t>
+          <t>COA-0002</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Metabolic / Research</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F43" t="n">
-        <v>51.88</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
-        <v>0.03760000000000005</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>99.369</v>
@@ -19986,27 +20796,25 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>46057</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>On label</t>
         </is>
       </c>
     </row>
@@ -20016,47 +20824,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COA-0042</t>
+          <t>COA-0049</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ipamorelin</t>
+          <t>5-Amino-1MQ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Growth Hormone Support</t>
+          <t>Metabolic / Research</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>5.17</v>
+        <v>51.88</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03399999999999999</v>
+        <v>0.03760000000000005</v>
       </c>
       <c r="H44" t="n">
-        <v>99.34</v>
+        <v>99.369</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>46239</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -20066,7 +20876,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -20076,34 +20886,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COA-0039</t>
+          <t>COA-0042</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Ipamorelin</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>5.07</v>
+        <v>5.17</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01400000000000006</v>
+        <v>0.03399999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>99.31999999999999</v>
+        <v>99.34</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -20116,7 +20926,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -20136,27 +20946,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COA-0048</t>
+          <t>COA-0039</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SS-31</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
-        <v>51.52</v>
+        <v>5.07</v>
       </c>
       <c r="G46" t="n">
-        <v>0.03040000000000006</v>
+        <v>0.01400000000000006</v>
       </c>
       <c r="H46" t="n">
         <v>99.31999999999999</v>
@@ -20168,17 +20978,15 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>46239</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -20188,7 +20996,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -20198,47 +21006,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COA-0037</t>
+          <t>COA-0048</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BPC-157 / TB-500 Blend</t>
+          <t>SS-31</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Healing / Recovery Blend</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F47" t="n">
-        <v>10.55</v>
+        <v>51.52</v>
       </c>
       <c r="G47" t="n">
-        <v>0.05500000000000007</v>
+        <v>0.03040000000000006</v>
       </c>
       <c r="H47" t="n">
-        <v>99.13</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>46239</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -20248,7 +21058,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</t>
+          <t>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -20258,57 +21068,57 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COA-0016</t>
+          <t>COA-0053</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TB-500</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>Cosmetic / Recovery</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F48" t="n">
-        <v>11.38</v>
+        <v>100.52</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1380000000000001</v>
+        <v>0.0052</v>
       </c>
       <c r="H48" t="n">
-        <v>99.08499999999999</v>
+        <v>99.25</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>Freedom Diagnostics</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>46155</v>
+        <v>46224</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>TB-500 / TB4</t>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
         </is>
       </c>
     </row>
@@ -20318,30 +21128,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COA-0014</t>
+          <t>COA-0037</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>BPC-157 / TB-500 Blend</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Healing / Recovery Blend</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>11.17</v>
+        <v>10.55</v>
       </c>
       <c r="G49" t="n">
-        <v>0.117</v>
+        <v>0.05500000000000007</v>
       </c>
       <c r="H49" t="n">
-        <v>99.05500000000001</v>
+        <v>99.13</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -20350,25 +21160,25 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>MS10 / MOTS-C</t>
+          <t>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -20378,34 +21188,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COA-0011</t>
+          <t>COA-0016</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cagrilintide</t>
+          <t>TB-500</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Healing / Recovery</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>10.47</v>
+        <v>11.38</v>
       </c>
       <c r="G50" t="n">
-        <v>0.04700000000000006</v>
+        <v>0.1380000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>99.04000000000001</v>
+        <v>99.08499999999999</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -20428,7 +21238,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>TB-500 / TB4</t>
         </is>
       </c>
     </row>
@@ -20438,27 +21248,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COA-0017</t>
+          <t>COA-0014</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BPC-157</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F51" t="n">
-        <v>5.54</v>
+        <v>11.17</v>
       </c>
       <c r="G51" t="n">
-        <v>0.108</v>
+        <v>0.117</v>
+      </c>
+      <c r="H51" t="n">
+        <v>99.05500000000001</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -20471,7 +21284,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>46057</v>
+        <v>46155</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -20485,7 +21298,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Blend report BPC5+TB5</t>
+          <t>MS10 / MOTS-C</t>
         </is>
       </c>
     </row>
@@ -20495,52 +21308,169 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>COA-0011</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cagrilintide</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>10</v>
+      </c>
+      <c r="F52" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.04700000000000006</v>
+      </c>
+      <c r="H52" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>46155</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>COA-0017</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BPC-157</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Healing / Recovery</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>46057</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Blend report BPC5+TB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>COA-0018</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>TB-500</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Healing / Recovery</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E54" t="n">
         <v>5</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F54" t="n">
         <v>5.43</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G54" t="n">
         <v>0.08599999999999994</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>On label</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Janoshik</t>
         </is>
       </c>
-      <c r="K52" t="n">
+      <c r="K54" t="n">
         <v>46057</v>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Not Listed</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Not Listed</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Blend report BPC5+TB5</t>
         </is>
@@ -20775,13 +21705,481 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99.446</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cjc-1295-no-dac-ipamorelin/CJC-1295-No-DAC-Ipamorelin-10mg-2026-08-08-Kovera.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>46224</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>100.52</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-07-21-Freedom.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25764,7 +27162,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Local image: assets/coa/images/kovera-labs/5-amino-1mq/5-Amino-1MQ-50mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/5-amino-1mq/5-Amino-1MQ-50mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -25818,16 +27216,16 @@
         <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>10.16</v>
+        <v>10.38</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="H51" t="n">
-        <v>99.639</v>
+        <v>99.849</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -25844,10 +27242,8 @@
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="L51" t="n">
+        <v>46242</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -25861,12 +27257,12 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Redacted</t>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Local image: assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-08-08-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -25876,12 +27272,12 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Unique supplied Kovera certificate image.</t>
+          <t>Replaces earlier transcription for the same supplied certificate image</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -25999,6 +27395,206 @@
       <c r="V52" t="inlineStr">
         <is>
           <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H53" t="n">
+        <v>99.446</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cjc-1295-no-dac-ipamorelin/CJC-1295-No-DAC-Ipamorelin-10mg-2026-08-08-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Unique product/batch/date record</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>46224</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-07-21-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Unique strength/accession/date record</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
         </is>
       </c>
     </row>
@@ -26247,7 +27843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30491,7 +32087,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITEM-0047</t>
+          <t>COA-0047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -30556,7 +32152,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/retatrutide/Retatrutide-60mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/retatrutide/Retatrutide-60mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
@@ -30583,7 +32179,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITEM-0048</t>
+          <t>COA-0048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -30648,7 +32244,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/ss-31/SS-31-50mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/ss-31/SS-31-50mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -30675,7 +32271,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ITEM-0049</t>
+          <t>COA-0049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -30767,7 +32363,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITEM-0050</t>
+          <t>COA-0050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -30784,55 +32380,53 @@
         <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>10.16</v>
+        <v>10.38</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="H51" t="n">
-        <v>99.639</v>
+        <v>99.849</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>COA-0050</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
           <t>Redacted</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>On label</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>COA-0050</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>Redacted</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Redacted</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-08-08-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
@@ -30852,14 +32446,14 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITEM-0051</t>
+          <t>COA-0051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -30924,7 +32518,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/dsip/DSIP-10mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/dsip/DSIP-10mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -30945,6 +32539,186 @@
       <c r="T52" t="inlineStr">
         <is>
           <t>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H53" t="n">
+        <v>99.446</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>46242</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cjc-1295-no-dac-ipamorelin/CJC-1295-No-DAC-Ipamorelin-10mg-2026-08-08-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>100</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>46224</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-07-21-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
         </is>
       </c>
     </row>
@@ -30959,7 +32733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31107,7 +32881,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -31202,7 +32976,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -31297,7 +33071,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -31392,7 +33166,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -31487,7 +33261,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -31582,7 +33356,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -31668,7 +33442,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -31763,7 +33537,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -31858,7 +33632,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -31953,7 +33727,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -32048,7 +33822,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -32143,7 +33917,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -32238,7 +34012,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -32333,7 +34107,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -32428,7 +34202,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -32523,7 +34297,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -32618,7 +34392,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -32710,7 +34484,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -32802,7 +34576,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -32897,7 +34671,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -32992,7 +34766,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -33087,7 +34861,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -33182,7 +34956,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -33277,7 +35051,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -33369,7 +35143,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -33461,7 +35235,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -33553,7 +35327,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -33650,7 +35424,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -33747,7 +35521,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -33844,7 +35618,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -33941,7 +35715,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -34038,7 +35812,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -34135,7 +35909,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -34232,7 +36006,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -34329,7 +36103,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -34426,7 +36200,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -34523,7 +36297,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -34618,7 +36392,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -34713,7 +36487,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -34808,7 +36582,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -34903,7 +36677,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -34998,7 +36772,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -35093,7 +36867,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -35188,7 +36962,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Report reviewed</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -35283,7 +37057,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -35378,7 +37152,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -35468,12 +37242,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/retatrutide/Retatrutide-60mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/retatrutide/Retatrutide-60mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -35565,12 +37339,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/ss-31/SS-31-50mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/ss-31/SS-31-50mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -35667,7 +37441,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -35759,28 +37533,28 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-07-29-Kovera.jpg</t>
+          <t>assets/coa/images/kovera-labs/cagrilintide/Cagrilintide-10mg-2026-08-08-Kovera.jpg</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I51" t="n">
         <v>10</v>
       </c>
       <c r="J51" t="n">
-        <v>10.16</v>
+        <v>10.38</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="L51" t="n">
-        <v>0.01600000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="M51" t="n">
-        <v>99.639</v>
+        <v>99.849</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
@@ -35789,13 +37563,11 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Redacted</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>CAGRI10-2608-01-PUR-SLV</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>46242</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -35804,7 +37576,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -35856,12 +37628,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>assets/coa/images/kovera-labs/dsip/DSIP-10mg-2026-07-29-Kovera.jpg</t>
+          <t>Local image: assets/coa/images/kovera-labs/dsip/DSIP-10mg-2026-07-29-Kovera.jpg</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -35917,6 +37689,196 @@
       <c r="U52" t="inlineStr">
         <is>
           <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>COA-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GHRH / GH Secretagogue Blend</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/cjc-1295-no-dac-ipamorelin/CJC-1295-No-DAC-Ipamorelin-10mg-2026-08-08-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="M53" t="n">
+        <v>99.446</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>CJCIPA10-2608-01-YEL-SLV</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>46242</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Yellow flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>COA-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2607170294</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/ghk-cu/GHK-Cu-100mg-2026-07-21-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>100</v>
+      </c>
+      <c r="J54" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="M54" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Light Blue Cap</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>46224</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
         </is>
       </c>
     </row>
@@ -35931,7 +37893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35969,7 +37931,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADAMAX</t>
+          <t>5-Amino-1MQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -36001,7 +37963,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AOD-9604</t>
+          <t>ADAMAX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -36033,7 +37995,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BPC-157</t>
+          <t>AOD-9604</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -36058,14 +38020,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GHRH analog</t>
+          <t>GHRH / GH Secretagogue Blend</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BPC-157 / TB-500 Blend</t>
+          <t>BPC-157</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -36085,14 +38047,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>GHRH analog</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BPC/TB Blend</t>
+          <t>BPC-157 / TB-500 Blend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -36107,14 +38069,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth Hormone Support</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CJC-1295</t>
+          <t>BPC/TB Blend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -36129,14 +38091,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CJC-1295 No DAC</t>
+          <t>CJC-1295</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -36151,14 +38113,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Healing / Recovery Blend</t>
+          <t>Healing / Recovery</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cagrilintide</t>
+          <t>CJC-1295 No DAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -36173,14 +38135,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Metabolic / Cellular Energy</t>
+          <t>Healing / Recovery Blend</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Eloralintide</t>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -36190,153 +38152,180 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Light Blue</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Metabolic / Fat Loss</t>
+          <t>Metabolic / Cellular Energy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GHK-Cu</t>
+          <t>Cagrilintide</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Metabolic / Fat Loss</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ipamorelin</t>
+          <t>DSIP</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KLOW 80mg</t>
+          <t>Eloralintide</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Royal Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Regenerative / Skin</t>
+          <t>Metabolic / Research</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transparent</t>
+          <t>Royal Blue</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Research Peptide</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Ipamorelin</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Transparent</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Regenerative / Skin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NAD+</t>
+          <t>KLOW 80mg</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Research Peptide</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>KPV</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sleep / Research</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SS-31</t>
+          <t>MOTS-C</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>NAD+</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TB-500</t>
+          <t>Retatrutide</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>SS-31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ</t>
+          <t>Semaglutide</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DSIP</t>
+          <t>TB-500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tirzepatide</t>
         </is>
       </c>
     </row>
@@ -36368,7 +38357,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -36383,7 +38371,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -36398,7 +38385,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -36413,7 +38399,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -36428,7 +38413,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -36443,7 +38427,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -36458,7 +38441,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -36473,7 +38455,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -36488,7 +38469,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -36503,7 +38483,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -39,6 +39,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0051" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0052" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +480,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -508,7 +510,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.59399999999999</v>
+        <v>99.602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -573,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -1236,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,7 +1403,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -6004,6 +6006,180 @@
       <c r="S66" t="inlineStr">
         <is>
           <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>20</v>
+      </c>
+      <c r="E67" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H67" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>40</v>
+      </c>
+      <c r="E68" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H68" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
         </is>
       </c>
     </row>
@@ -10447,7 +10623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15863,6 +16039,210 @@
       <c r="V54" t="inlineStr">
         <is>
           <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20</v>
+      </c>
+      <c r="E55" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H55" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-20mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Unique client/accession/date record</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-40mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Unique client/accession/date record</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21473,6 +21853,130 @@
       <c r="N54" t="inlineStr">
         <is>
           <t>Blend report BPC5+TB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>20</v>
+      </c>
+      <c r="F55" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H55" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>40</v>
+      </c>
+      <c r="F56" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
         </is>
       </c>
     </row>
@@ -22173,13 +22677,485 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-20mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compound</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>43.16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>99.90000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-40mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27595,6 +28571,210 @@
       <c r="V54" t="inlineStr">
         <is>
           <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20</v>
+      </c>
+      <c r="E55" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H55" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-20mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Unique client/accession/date record</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-40mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Unique client/accession/date record</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
         </is>
       </c>
     </row>
@@ -27843,7 +29023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T54"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32719,6 +33899,190 @@
       <c r="T54" t="inlineStr">
         <is>
           <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>20</v>
+      </c>
+      <c r="E55" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H55" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-20mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40</v>
+      </c>
+      <c r="E56" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-40mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
         </is>
       </c>
     </row>
@@ -32733,7 +34097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U54"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37879,6 +39243,200 @@
       <c r="U54" t="inlineStr">
         <is>
           <t>Light-blue flip-off cap; silver aluminum crimp visible in the supplied COA vial image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>COA-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2608250163</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-20mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>20</v>
+      </c>
+      <c r="J55" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M55" t="n">
+        <v>99.72</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Clear Pink Cap</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Clear Pink</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Clear pink flip-off cap, per vial image and 'Clear Pink Cap' lot description on the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>COA-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2608250164</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>assets/coa/images/freedom-diagnostics/retatrutide/Retatrutide-40mg-2026-08-29-Freedom.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>40</v>
+      </c>
+      <c r="J56" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="M56" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Clear Purple Cap</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Clear purple flip-off cap, per vial image and 'Clear Purple Cap' lot description on the COA.</t>
         </is>
       </c>
     </row>

--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -41,8 +41,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0053" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0054" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0055" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0056" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0057" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0058" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0059" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0060" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0061" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COA_COA_0062" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dashboard'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COA Database'!$A$1:$V$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Purity Rankings'!$A$1:$N$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Batch History'!$A$1:$V$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Inventory'!$A$1:$T$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Certificates'!$A$1:$U$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'COA Status'!$A$1:$S$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="32" hidden="1">'COA_COA_0054'!$A$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="33" hidden="1">'COA_COA_0055'!$A$1:$B$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="34" hidden="1">'COA_COA_0056'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="35" hidden="1">'COA_COA_0057'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="36" hidden="1">'COA_COA_0058'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="37" hidden="1">'COA_COA_0059'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="38" hidden="1">'COA_COA_0060'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="39" hidden="1">'COA_COA_0061'!$A$1:$B$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="40" hidden="1">'COA_COA_0062'!$A$1:$B$31</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -480,7 +504,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -495,11 +519,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
+          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Glutathione, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, Semax, Sermorelin, TB-500, Tesamorelin, Tirzepatide</t>
         </is>
       </c>
     </row>
@@ -510,7 +534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>99.602</v>
+        <v>99.601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -525,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +569,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -555,11 +579,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</t>
+          <t>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, Pristin Biotech, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</t>
         </is>
       </c>
     </row>
@@ -571,7 +595,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1229,6 +1253,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1239,7 +1264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S68"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,7 +1298,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1288,11 +1313,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, TB-500, Tirzepatide</t>
+          <t>5-Amino-1MQ, ADAMAX, AOD-9604, BPC-157, BPC-157 / TB-500 Blend, BPC/TB Blend, CJC-1295, CJC-1295 No DAC, CJC-1295 No DAC / Ipamorelin, Cagrilintide, DSIP, Eloralintide, GHK-Cu, Glutathione, Ipamorelin, KLOW 80mg, KPV, MOTS-C, NAD+, Retatrutide, SS-31, Semaglutide, Semax, Sermorelin, TB-500, Tesamorelin, Tirzepatide</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1328,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1318,7 +1343,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1348,7 +1373,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,7 +1388,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99.59399999999999</v>
+        <v>99.601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1378,11 +1403,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</t>
+          <t>Aminos Analytics, BT Labs, Freedom Diagnostics, ILS Laboratories, Janoshik, Kovera Labs, Pristin Biotech, SteriGenix, Testides, Tianjin Qiangxin (third-party partner lab)</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1419,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1403,6 +1428,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -6183,7 +6209,617 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H69" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>30</v>
+      </c>
+      <c r="E70" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+      <c r="H70" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1478.47</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-21.53</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+      <c r="H72" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="H73" t="n">
+        <v>99.568</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="H74" t="n">
+        <v>99.33499999999999</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H75" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:S75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10623,7 +11259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16246,7 +16882,722 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H57" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/tesamorelin/Tesamorelin-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+      <c r="H58" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-30mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H59" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1478.47</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-21.53</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/glutathione/Glutathione-1500mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="H61" t="n">
+        <v>99.568</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/semax/Semax-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>99.33499999999999</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/sermorelin/Sermorelin-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H63" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-353561-SteriGenix.pdf</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:V63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18579,7 +19930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18842,57 +20193,59 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>COA-0021</t>
+          <t>COA-0055</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CJC-1295 No DAC</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Growth Hormone Support</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>9.66</v>
+        <v>43.16</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.03399999999999999</v>
+        <v>0.079</v>
       </c>
       <c r="H5" t="n">
-        <v>99.89700000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>46156</v>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Clear Purple</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Not Listed</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Not Listed</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mod GRF 1-29</t>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
         </is>
       </c>
     </row>
@@ -18902,34 +20255,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COA-0012</t>
+          <t>COA-0021</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AOD-9604</t>
+          <t>CJC-1295 No DAC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Metabolic / Fat Loss</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>5.95</v>
+        <v>9.66</v>
       </c>
       <c r="G6" t="n">
-        <v>0.19</v>
+        <v>-0.03399999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>99.883</v>
+        <v>99.89700000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -18952,7 +20305,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>rHGH fragment / AOD-9604</t>
+          <t>Mod GRF 1-29</t>
         </is>
       </c>
     </row>
@@ -18962,30 +20315,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>COA-0024</t>
+          <t>COA-0012</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>AOD-9604</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Metabolic / Fat Loss</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>22.47</v>
+        <v>5.95</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1234999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="H7" t="n">
-        <v>99.86</v>
+        <v>99.883</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -18994,17 +20347,15 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-06-14</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>46156</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Clear Green</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -19014,7 +20365,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</t>
+          <t>rHGH fragment / AOD-9604</t>
         </is>
       </c>
     </row>
@@ -19024,57 +20375,59 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>COA-0050</t>
+          <t>COA-0024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cagrilintide</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Amylin / Weight</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>10.38</v>
+        <v>22.47</v>
       </c>
       <c r="G8" t="n">
-        <v>0.038</v>
+        <v>0.1234999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>99.849</v>
+        <v>99.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>46242</v>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Clear Green</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
+          <t>Retatrutide 20mg, separate batch from existing Retatrutide records; received 06/11/2026, reported 06/14/2026.</t>
         </is>
       </c>
     </row>
@@ -19084,30 +20437,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COA-0013</t>
+          <t>COA-0057</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>10.58</v>
+        <v>37.37</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05800000000000001</v>
+        <v>0.2456666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>99.84699999999999</v>
+        <v>99.86</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -19116,11 +20469,13 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>46057</v>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -19134,7 +20489,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10 mg label</t>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
         </is>
       </c>
     </row>
@@ -19144,57 +20499,57 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COA-0010</t>
+          <t>COA-0050</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>Cagrilintide</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Amylin / Weight</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>32.5</v>
+        <v>10.38</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.038</v>
       </c>
       <c r="H10" t="n">
-        <v>99.84</v>
+        <v>99.849</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>46059</v>
+        <v>46242</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>30 mg label</t>
+          <t>Identity confirmed as Cagrilintide by LC-MS. Endotoxin PASS; microbial sterility: No Growth. Vial 1: 99.827% / 10.29 mg; vial 2: 99.871% / 10.46 mg. Certified 08/08/2026.</t>
         </is>
       </c>
     </row>
@@ -19204,30 +20559,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COA-0022</t>
+          <t>COA-0013</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>34.77</v>
+        <v>10.58</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1590000000000001</v>
+        <v>0.05800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>99.825</v>
+        <v>99.84699999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -19240,7 +20595,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>46156</v>
+        <v>46057</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -19254,7 +20609,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</t>
+          <t>10 mg label</t>
         </is>
       </c>
     </row>
@@ -19264,30 +20619,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COA-0036</t>
+          <t>COA-0010</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KLOW 80mg</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Healing / Recovery Blend</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>96.45999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.20575</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>99.81999999999999</v>
+        <v>99.84</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -19296,27 +20651,25 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>46059</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</t>
+          <t>30 mg label</t>
         </is>
       </c>
     </row>
@@ -19326,43 +20679,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COA-0015</t>
+          <t>COA-0058</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>38.96</v>
+        <v>10.8</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.02599999999999998</v>
+        <v>0.08</v>
       </c>
       <c r="H13" t="n">
-        <v>99.813</v>
+        <v>99.83</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>46057</v>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -19376,7 +20731,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>40 mg label</t>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
         </is>
       </c>
     </row>
@@ -19386,30 +20741,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COA-0028</t>
+          <t>COA-0022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BPC/TB Blend</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>11.85</v>
+        <v>34.77</v>
       </c>
       <c r="G14" t="n">
-        <v>0.185</v>
+        <v>0.1590000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>99.81</v>
+        <v>99.825</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -19418,13 +20773,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Testides</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>46156</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -19438,7 +20791,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>RT30 Retatrutide 30mg; common GLP-1 blind test; overfilled.</t>
         </is>
       </c>
     </row>
@@ -19448,30 +20801,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COA-0009</t>
+          <t>COA-0036</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>KLOW 80mg</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Healing / Recovery Blend</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F15" t="n">
-        <v>65.09999999999999</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08499999999999991</v>
+        <v>0.20575</v>
       </c>
       <c r="H15" t="n">
-        <v>99.8</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -19480,25 +20833,27 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>BT Labs</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>46133</v>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>60 mg label; 108.5% potency</t>
+          <t>Identity confirmed: GHK-Cu/KPV/BPC-157/Thymosin Beta-4. Net content: GHK-Cu 62.93 mg; KPV 9.09 mg; BPC-157 12.40 mg; Thymosin Beta-4 12.04 mg. Blue lyophilized powder. Received 07/17/2026; reported 07/20/2026.</t>
         </is>
       </c>
     </row>
@@ -19508,57 +20863,57 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>COA-0041</t>
+          <t>COA-0015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GHK-Cu</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cosmetic / Recovery</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F16" t="n">
-        <v>51.34</v>
+        <v>38.96</v>
       </c>
       <c r="G16" t="n">
-        <v>0.02680000000000007</v>
+        <v>-0.02599999999999998</v>
       </c>
       <c r="H16" t="n">
-        <v>99.78</v>
+        <v>99.813</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
+          <t>Janoshik</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>46239</v>
+        <v>46057</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>40 mg label</t>
         </is>
       </c>
     </row>
@@ -19568,59 +20923,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COA-0035</t>
+          <t>COA-0028</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GHK-Cu</t>
+          <t>BPC/TB Blend</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Regenerative / Skin</t>
+          <t>Healing / Recovery</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>50.75</v>
+        <v>11.85</v>
       </c>
       <c r="G17" t="n">
-        <v>0.015</v>
+        <v>0.185</v>
       </c>
       <c r="H17" t="n">
-        <v>99.77</v>
+        <v>99.81</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
+          <t>Testides</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Clear/Transparent</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</t>
+          <t>BPC-157 5.76mg + TB-500 6.09mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -19630,7 +20985,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COA-0034</t>
+          <t>COA-0009</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -19644,45 +20999,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F18" t="n">
-        <v>15.59</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03933333333333333</v>
+        <v>0.08499999999999991</v>
       </c>
       <c r="H18" t="n">
-        <v>99.747</v>
+        <v>99.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
+          <t>BT Labs</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>46133</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
+          <t>60 mg label; 108.5% potency</t>
         </is>
       </c>
     </row>
@@ -19692,30 +21045,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COA-0023</t>
+          <t>COA-0056</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>Tesamorelin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>16.18</v>
+        <v>12.18</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07866666666666665</v>
+        <v>0.218</v>
       </c>
       <c r="H19" t="n">
-        <v>99.73099999999999</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -19724,11 +21077,13 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>46156</v>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -19742,7 +21097,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</t>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
         </is>
       </c>
     </row>
@@ -19752,30 +21107,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COA-0045</t>
+          <t>COA-0041</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CJC-1295</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GHRH analog</t>
+          <t>Cosmetic / Recovery</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F20" t="n">
-        <v>10.52</v>
+        <v>51.34</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05199999999999996</v>
+        <v>0.02680000000000007</v>
       </c>
       <c r="H20" t="n">
-        <v>99.72</v>
+        <v>99.78</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -19784,25 +21139,25 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ILS Laboratories</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</t>
+          <t>Reported as GHK-Cu (Copper Peptide); identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -19812,57 +21167,59 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COA-0007</t>
+          <t>COA-0035</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Regenerative / Skin</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>50.75</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3</v>
+        <v>0.015</v>
       </c>
       <c r="H21" t="n">
-        <v>99.7</v>
+        <v>99.77</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>BT Labs</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>46133</v>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Royal Blue</t>
+          <t>Clear/Transparent</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>20 mg label; 130.1% potency</t>
+          <t>GHK-Cu 50mg; identity confirmed; blue lyophilized powder; received 06/26/2026; reported 06/29/2026.</t>
         </is>
       </c>
     </row>
@@ -19872,7 +21229,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COA-0008</t>
+          <t>COA-0034</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -19886,43 +21243,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>46.6</v>
+        <v>15.59</v>
       </c>
       <c r="G22" t="n">
-        <v>0.165</v>
+        <v>0.03933333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>99.7</v>
+        <v>99.747</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>BT Labs</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>46106</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40 mg label; 116.4% potency</t>
+          <t>Kovera image COA; purple cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
         </is>
       </c>
     </row>
@@ -19932,43 +21291,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COA-0044</t>
+          <t>COA-0023</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eloralintide</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Amylin / Weight</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>4.63</v>
+        <v>16.18</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.07400000000000002</v>
+        <v>0.07866666666666665</v>
       </c>
       <c r="H23" t="n">
-        <v>99.67</v>
+        <v>99.73099999999999</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Underfilled</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Tianjin Qiangxin (third-party partner lab)</t>
+          <t>Janoshik</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>46234</v>
+        <v>46156</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -19982,7 +21341,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</t>
+          <t>T15 Tirzepatide 15mg; common GLP-1 blind test; overfilled.</t>
         </is>
       </c>
     </row>
@@ -19992,30 +21351,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>COA-0003</t>
+          <t>COA-0045</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>CJC-1295</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>GHRH analog</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>6.63</v>
+        <v>10.52</v>
       </c>
       <c r="G24" t="n">
-        <v>0.326</v>
+        <v>0.05199999999999996</v>
       </c>
       <c r="H24" t="n">
-        <v>99.654</v>
+        <v>99.72</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -20024,11 +21383,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>ILS Laboratories</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>46174</v>
+        <v>46234</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -20042,7 +21401,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Heavy metals negative; endotoxin pass</t>
+          <t>Accession ACC-2026-10918. Identity confirmed by HPLC-RTM; fentanyl screen not detected. Analysis 07/31/2026; received 07/17/2026; lyophilized sample, 3 mL. COA/access identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -20052,12 +21411,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>COA-0032</t>
+          <t>COA-0054</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20066,45 +21425,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
-        <v>15.53</v>
+        <v>21.94</v>
       </c>
       <c r="G25" t="n">
-        <v>0.03533333333333333</v>
+        <v>0.097</v>
       </c>
       <c r="H25" t="n">
-        <v>99.642</v>
+        <v>99.72</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>Freedom Diagnostics</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Clear Pink</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</t>
+          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
         </is>
       </c>
     </row>
@@ -20114,7 +21473,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COA-0033</t>
+          <t>COA-0007</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -20128,16 +21487,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>33.24</v>
+        <v>26</v>
       </c>
       <c r="G26" t="n">
-        <v>0.108</v>
+        <v>0.3</v>
       </c>
       <c r="H26" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -20146,27 +21505,25 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
+          <t>BT Labs</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>46133</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Royal Blue</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
+          <t>20 mg label; 130.1% potency</t>
         </is>
       </c>
     </row>
@@ -20176,12 +21533,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COA-0047</t>
+          <t>COA-0008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20190,16 +21547,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F27" t="n">
-        <v>63.37</v>
+        <v>46.6</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05616666666666662</v>
+        <v>0.165</v>
       </c>
       <c r="H27" t="n">
-        <v>99.59</v>
+        <v>99.7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -20208,27 +21565,25 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+          <t>BT Labs</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>46106</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Gray</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>40 mg label; 116.4% potency</t>
         </is>
       </c>
     </row>
@@ -20238,43 +21593,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COA-0020</t>
+          <t>COA-0044</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KPV</t>
+          <t>Eloralintide</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Amylin / Weight</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>12.19</v>
+        <v>4.63</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2189999999999999</v>
+        <v>-0.07400000000000002</v>
       </c>
       <c r="H28" t="n">
-        <v>99.589</v>
+        <v>99.67</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>Underfilled</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>Tianjin Qiangxin (third-party partner lab)</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>46057</v>
+        <v>46234</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -20288,7 +21643,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>Report identifies sample as Elor5/Eloralintide. LCMS/HPLC purity 99.67%; peptide weight 4.63 mg. Report states neither issuer nor partner lab holds CMA/CNAS accreditation.</t>
         </is>
       </c>
     </row>
@@ -20298,7 +21653,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COA-0031</t>
+          <t>COA-0003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -20312,16 +21667,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>33.77</v>
+        <v>6.63</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1256666666666667</v>
+        <v>0.326</v>
       </c>
       <c r="H29" t="n">
-        <v>99.58</v>
+        <v>99.654</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -20330,13 +21685,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Testides</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>46174</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -20350,7 +21703,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>Heavy metals negative; endotoxin pass</t>
         </is>
       </c>
     </row>
@@ -20360,47 +21713,49 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COA-0040</t>
+          <t>COA-0032</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BPC-157</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>5.13</v>
+        <v>15.53</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02599999999999998</v>
+        <v>0.03533333333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>99.56999999999999</v>
+        <v>99.642</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>46239</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -20410,7 +21765,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Kovera image COA; black cap / silver crimp; heavy metals negative; endotoxin pass. CAS 910463-68-2 visible; report/access code redacted.</t>
         </is>
       </c>
     </row>
@@ -20420,12 +21775,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COA-0026</t>
+          <t>COA-0033</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -20434,16 +21789,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
-        <v>42.53</v>
+        <v>33.24</v>
       </c>
       <c r="G31" t="n">
-        <v>0.06325</v>
+        <v>0.108</v>
       </c>
       <c r="H31" t="n">
-        <v>99.569</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -20457,7 +21812,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -20472,7 +21827,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Blue cap Retatrutide 40mg</t>
+          <t>Kovera image COA; blue cap / silver crimp; heavy metals negative; endotoxin pass. CAS 2023788-19-2 visible; report/access code redacted.</t>
         </is>
       </c>
     </row>
@@ -20482,7 +21837,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COA-0025</t>
+          <t>COA-0047</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -20496,16 +21851,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F32" t="n">
-        <v>33.31</v>
+        <v>63.37</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1103333333333333</v>
+        <v>0.05616666666666662</v>
       </c>
       <c r="H32" t="n">
-        <v>99.563</v>
+        <v>99.59</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -20519,12 +21874,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Transparent</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -20534,7 +21889,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Transparent cap Retatrutide 30mg</t>
+          <t>Identity confirmed as Retatrutide by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -20544,57 +21899,57 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COA-0046</t>
+          <t>COA-0020</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NAD+</t>
+          <t>KPV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Metabolic / Cellular Energy</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>488.47</v>
+        <v>12.19</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.02305999999999995</v>
+        <v>0.2189999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>99.54900000000001</v>
+        <v>99.589</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>Janoshik</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>46232</v>
+        <v>46057</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</t>
+          <t>Overfilled</t>
         </is>
       </c>
     </row>
@@ -20604,12 +21959,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COA-0038</t>
+          <t>COA-0031</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tirzepatide</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20618,43 +21973,45 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F34" t="n">
-        <v>10.09</v>
+        <v>33.77</v>
       </c>
       <c r="G34" t="n">
-        <v>0.008999999999999985</v>
+        <v>0.1256666666666667</v>
       </c>
       <c r="H34" t="n">
-        <v>99.52</v>
+        <v>99.58</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>46239</v>
+          <t>Testides</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Retatrutide 30mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -20664,30 +22021,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COA-0001</t>
+          <t>COA-0040</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>BPC-157</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Healing / Recovery</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>11.8</v>
+        <v>5.13</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1800000000000001</v>
+        <v>0.02599999999999998</v>
       </c>
       <c r="H35" t="n">
-        <v>99.51600000000001</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -20696,25 +22053,25 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>46156</v>
+        <v>46239</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>RT10 - common GLP-1 blind test; overfilled</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +22081,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COA-0006</t>
+          <t>COA-0026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -20737,38 +22094,46 @@
           <t>GLP-1 / Weight</t>
         </is>
       </c>
+      <c r="E36" t="n">
+        <v>40</v>
+      </c>
       <c r="F36" t="n">
-        <v>22.47</v>
+        <v>42.53</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.06325</v>
       </c>
       <c r="H36" t="n">
-        <v>99.5</v>
+        <v>99.569</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Aminos Analytics</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>46146</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Labeled quantity unclear from image</t>
+          <t>Blue cap Retatrutide 40mg</t>
         </is>
       </c>
     </row>
@@ -20778,34 +22143,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COA-0004</t>
+          <t>COA-0060</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>Semax</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Nootropic / Research</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>17.93</v>
+        <v>9.65</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1953333333333333</v>
+        <v>-0.035</v>
       </c>
       <c r="H37" t="n">
-        <v>99.491</v>
+        <v>99.568</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -20813,22 +22178,24 @@
           <t>Kovera Labs</t>
         </is>
       </c>
-      <c r="K37" t="n">
-        <v>46175</v>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Heavy metals negative; endotoxin pass</t>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
         </is>
       </c>
     </row>
@@ -20838,7 +22205,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COA-0030</t>
+          <t>COA-0025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -20852,16 +22219,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>21.4</v>
+        <v>33.31</v>
       </c>
       <c r="G38" t="n">
-        <v>0.06999999999999999</v>
+        <v>0.1103333333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>99.48999999999999</v>
+        <v>99.563</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -20870,27 +22237,27 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Testides</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Transparent</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>Transparent cap Retatrutide 30mg</t>
         </is>
       </c>
     </row>
@@ -20900,30 +22267,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COA-0051</t>
+          <t>COA-0046</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DSIP</t>
+          <t>NAD+</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sleep / Research</t>
+          <t>Metabolic / Cellular Energy</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F39" t="n">
-        <v>10.16</v>
+        <v>488.47</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01600000000000001</v>
+        <v>-0.02305999999999995</v>
       </c>
       <c r="H39" t="n">
-        <v>99.464</v>
+        <v>99.54900000000001</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -20935,14 +22302,12 @@
           <t>Kovera Labs</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="K39" t="n">
+        <v>46232</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -20952,7 +22317,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Identity confirmed as NAD+. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch conformity: vial 1 = 99.517% / 483.68 mg; vial 2 = 99.582% / 493.26 mg. Certified 07/29/2026. Report/access and batch identifiers are redacted.</t>
         </is>
       </c>
     </row>
@@ -20962,30 +22327,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COA-0052</t>
+          <t>COA-0038</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CJC-1295 No DAC / Ipamorelin</t>
+          <t>Tirzepatide</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GHRH / GH Secretagogue Blend</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>10</v>
       </c>
       <c r="F40" t="n">
-        <v>10.42</v>
+        <v>10.09</v>
       </c>
       <c r="G40" t="n">
-        <v>0.042</v>
+        <v>0.008999999999999985</v>
       </c>
       <c r="H40" t="n">
-        <v>99.446</v>
+        <v>99.52</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -20994,11 +22359,11 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Kovera Labs</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>46242</v>
+        <v>46239</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -21012,7 +22377,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -21022,7 +22387,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COA-0043</t>
+          <t>COA-0001</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -21039,13 +22404,13 @@
         <v>10</v>
       </c>
       <c r="F41" t="n">
-        <v>10.36</v>
+        <v>11.8</v>
       </c>
       <c r="G41" t="n">
-        <v>0.03599999999999994</v>
+        <v>0.1800000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>99.41</v>
+        <v>99.51600000000001</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -21054,25 +22419,25 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
+          <t>Janoshik</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>46239</v>
+        <v>46156</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>RT10 - common GLP-1 blind test; overfilled</t>
         </is>
       </c>
     </row>
@@ -21082,59 +22447,59 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COA-0029</t>
+          <t>COA-0059</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>Glutathione</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Antioxidant / Cellular Support</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>40</v>
+        <v>1500</v>
       </c>
       <c r="F42" t="n">
-        <v>45.03</v>
+        <v>1478.47</v>
       </c>
       <c r="G42" t="n">
-        <v>0.12575</v>
+        <v>-0.01435333333333333</v>
       </c>
       <c r="H42" t="n">
-        <v>99.39</v>
+        <v>99.51300000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Testides</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
         </is>
       </c>
     </row>
@@ -21144,7 +22509,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COA-0002</t>
+          <t>COA-0006</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -21157,30 +22522,24 @@
           <t>GLP-1 / Weight</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>10</v>
-      </c>
       <c r="F43" t="n">
-        <v>10</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
+        <v>22.47</v>
       </c>
       <c r="H43" t="n">
-        <v>99.369</v>
+        <v>99.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>Aminos Analytics</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>46057</v>
+        <v>46146</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -21194,7 +22553,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Labeled quantity unclear from image</t>
         </is>
       </c>
     </row>
@@ -21204,34 +22563,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COA-0049</t>
+          <t>COA-0004</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5-Amino-1MQ</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Metabolic / Research</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="F44" t="n">
-        <v>51.88</v>
+        <v>17.93</v>
       </c>
       <c r="G44" t="n">
-        <v>0.03760000000000005</v>
+        <v>0.1953333333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>99.369</v>
+        <v>99.491</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -21239,24 +22598,22 @@
           <t>Kovera Labs</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="K44" t="n">
+        <v>46175</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Heavy metals negative; endotoxin pass</t>
         </is>
       </c>
     </row>
@@ -21266,30 +22623,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COA-0042</t>
+          <t>COA-0030</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ipamorelin</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Growth Hormone Support</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>5.17</v>
+        <v>21.4</v>
       </c>
       <c r="G45" t="n">
-        <v>0.03399999999999999</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>99.34</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -21298,25 +22655,27 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>46239</v>
+          <t>Testides</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Retatrutide 20mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -21326,30 +22685,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COA-0039</t>
+          <t>COA-0051</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Semaglutide</t>
+          <t>DSIP</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Sleep / Research</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F46" t="n">
-        <v>5.07</v>
+        <v>10.16</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01400000000000006</v>
+        <v>0.01600000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>99.31999999999999</v>
+        <v>99.464</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -21358,15 +22717,17 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>46239</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -21376,7 +22737,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
+          <t>Identity confirmed as DSIP by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -21386,30 +22747,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COA-0048</t>
+          <t>COA-0052</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SS-31</t>
+          <t>CJC-1295 No DAC / Ipamorelin</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>GHRH / GH Secretagogue Blend</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F47" t="n">
-        <v>51.52</v>
+        <v>10.42</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03040000000000006</v>
+        <v>0.042</v>
       </c>
       <c r="H47" t="n">
-        <v>99.31999999999999</v>
+        <v>99.446</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -21421,14 +22782,12 @@
           <t>Kovera Labs</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
+      <c r="K47" t="n">
+        <v>46242</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Purple</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -21438,7 +22797,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
+          <t>Blend identity confirmed by LC-MS. Component analysis: Ipamorelin labeled 5 mg / measured 5.84 mg; CJC-1295 No DAC labeled 5 mg / measured 4.71 mg. Endotoxin PASS; microbial sterility: No Growth.</t>
         </is>
       </c>
     </row>
@@ -21448,57 +22807,57 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>COA-0053</t>
+          <t>COA-0043</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GHK-Cu</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cosmetic / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>100.52</v>
+        <v>10.36</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0052</v>
+        <v>0.03599999999999994</v>
       </c>
       <c r="H48" t="n">
-        <v>99.25</v>
+        <v>99.41</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Light Blue</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -21508,30 +22867,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COA-0037</t>
+          <t>COA-0029</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BPC-157 / TB-500 Blend</t>
+          <t>MOTS-C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Healing / Recovery Blend</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F49" t="n">
-        <v>10.55</v>
+        <v>45.03</v>
       </c>
       <c r="G49" t="n">
-        <v>0.05500000000000007</v>
+        <v>0.12575</v>
       </c>
       <c r="H49" t="n">
-        <v>99.13</v>
+        <v>99.39</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -21540,25 +22899,27 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>SteriGenix</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>46239</v>
+          <t>Testides</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Not Listed</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</t>
+          <t>MOTS-c 40mg; Date received/reported Jun 24, 2026; generated Jul 4, 2026.</t>
         </is>
       </c>
     </row>
@@ -21568,34 +22929,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COA-0016</t>
+          <t>COA-0002</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TB-500</t>
+          <t>Retatrutide</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>11.38</v>
+        <v>10</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1380000000000001</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>99.08499999999999</v>
+        <v>99.369</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -21604,7 +22965,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>46155</v>
+        <v>46057</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -21618,7 +22979,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>TB-500 / TB4</t>
+          <t>On label</t>
         </is>
       </c>
     </row>
@@ -21628,57 +22989,59 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COA-0014</t>
+          <t>COA-0049</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MOTS-C</t>
+          <t>5-Amino-1MQ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Metabolic / Mito</t>
+          <t>Metabolic / Research</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>11.17</v>
+        <v>51.88</v>
       </c>
       <c r="G51" t="n">
-        <v>0.117</v>
+        <v>0.03760000000000005</v>
       </c>
       <c r="H51" t="n">
-        <v>99.05500000000001</v>
+        <v>99.369</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>46155</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>MS10 / MOTS-C</t>
+          <t>Identity confirmed as 5-Amino-1MQ by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -21688,57 +23051,57 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COA-0011</t>
+          <t>COA-0042</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cagrilintide</t>
+          <t>Ipamorelin</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F52" t="n">
-        <v>10.47</v>
+        <v>5.17</v>
       </c>
       <c r="G52" t="n">
-        <v>0.04700000000000006</v>
+        <v>0.03399999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>99.04000000000001</v>
+        <v>99.34</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>On label</t>
+          <t>Overfilled</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>46155</v>
+        <v>46239</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>White</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -21748,54 +23111,59 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COA-0017</t>
+          <t>COA-0061</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BPC-157</t>
+          <t>Sermorelin</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>Growth Hormone Support</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>5.54</v>
+        <v>10.41</v>
       </c>
       <c r="G53" t="n">
-        <v>0.108</v>
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>99.33499999999999</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Janoshik</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>46057</v>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Blend report BPC5+TB5</t>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
         </is>
       </c>
     </row>
@@ -21805,27 +23173,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COA-0018</t>
+          <t>COA-0039</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TB-500</t>
+          <t>Semaglutide</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Healing / Recovery</t>
+          <t>GLP-1 / Weight</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>5.43</v>
+        <v>5.07</v>
       </c>
       <c r="G54" t="n">
-        <v>0.08599999999999994</v>
+        <v>0.01400000000000006</v>
+      </c>
+      <c r="H54" t="n">
+        <v>99.31999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -21834,25 +23205,25 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Janoshik</t>
+          <t>SteriGenix</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>46057</v>
+        <v>46239</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Blend report BPC5+TB5</t>
+          <t>Identity confirmed by LC-MS. Heavy metals and batch conformity: no data.</t>
         </is>
       </c>
     </row>
@@ -21862,59 +23233,59 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COA-0054</t>
+          <t>COA-0048</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>SS-31</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>GLP-1 / Weight</t>
+          <t>Metabolic / Mito</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>21.94</v>
+        <v>51.52</v>
       </c>
       <c r="G55" t="n">
-        <v>0.097</v>
+        <v>0.03040000000000006</v>
       </c>
       <c r="H55" t="n">
-        <v>99.72</v>
+        <v>99.31999999999999</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Overfilled</t>
+          <t>On label</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Freedom Diagnostics</t>
+          <t>Kovera Labs</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Clear Pink</t>
+          <t>Purple</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Not Listed</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 21.94 mg. Client: Tomcat Peptides. Accession 2608250163; received 08/25/2026; reported 08/29/2026.</t>
+          <t>Identity confirmed as SS-31 by LC-MS. Endotoxin safety screen PASS. Heavy metals arsenic, cadmium, lead, and mercury negative. Batch average from two-vial conformity results. Certified 07/29/2026; report, client, CAS, and batch identifiers are redacted in the supplied image.</t>
         </is>
       </c>
     </row>
@@ -21924,63 +23295,478 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>COA-0055</t>
+          <t>COA-0053</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Retatrutide</t>
+          <t>GHK-Cu</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100</v>
+      </c>
+      <c r="F56" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H56" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Freedom Diagnostics</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>46224</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Light Blue</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu by LC-MS. Blue lyophilized powder. Endotoxin replicates PASS; microbial analysis (PCR) PASS / no detectable microbial DNA. Received 07/17/2026; reported 07/21/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H57" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>COA-0037</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BPC-157 / TB-500 Blend</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Healing / Recovery Blend</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.05500000000000007</v>
+      </c>
+      <c r="H58" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>46239</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Identity confirmed by LC-MS. Component content reported as 5.37 mg BPC-157 and 5.18 mg TB-500; total 10.55 mg. Heavy metals and batch conformity: no data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>COA-0016</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TB-500</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Healing / Recovery</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.1380000000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>99.08499999999999</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>46155</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TB-500 / TB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>COA-0014</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MOTS-C</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Metabolic / Mito</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99.05500000000001</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>46155</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>MS10 / MOTS-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COA-0011</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cagrilintide</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>GLP-1 / Weight</t>
         </is>
       </c>
-      <c r="E56" t="n">
-        <v>40</v>
-      </c>
-      <c r="F56" t="n">
-        <v>43.16</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H56" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="I56" t="inlineStr">
+      <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.04700000000000006</v>
+      </c>
+      <c r="H61" t="n">
+        <v>99.04000000000001</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>46155</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>Overfilled</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Freedom Diagnostics</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Clear Purple</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COA-0017</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BPC-157</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Healing / Recovery</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>46057</v>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>Not Listed</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Identity confirmed as Retatrutide (GLP RT) by LC-MS; purity by HPLC-UV. White lyophilized powder. Net content 43.16 mg. Client: Tomcat Peptides. Accession 2608250164; received 08/25/2026; reported 08/29/2026.</t>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Blend report BPC5+TB5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>COA-0018</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TB-500</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Healing / Recovery</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.08599999999999994</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Janoshik</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>46057</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Blend report BPC5+TB5</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22909,6 +24695,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23145,6 +24932,1480 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.218</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.79000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/tesamorelin/Tesamorelin-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>37.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.86</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-30mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.83</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1478.47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-21.53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.51300000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confirmed: Glutathione (LC-MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lyophilized Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Endotoxin Safety Screen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Microbial Sterility Screen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>No Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Heavy Metals</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arsenic, Cadmium, Lead, Mercury: Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vial 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>99.246% purity / 1464.59 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vial 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>99.781% purity / 1492.36 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/glutathione/Glutathione-1500mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B28"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.035</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.568</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confirmed: Semax (LC-MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lyophilized Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Endotoxin Safety Screen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Microbial Sterility Screen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>No Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Heavy Metals</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arsenic, Cadmium, Lead, Mercury: Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vial 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>99.328% purity / 9.56 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vial 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>99.808% purity / 9.74 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/semax/Semax-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -23155,7 +26416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28778,7 +32039,1448 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H57" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/tesamorelin/Tesamorelin-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+      <c r="H58" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-30mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H59" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1478.47</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-21.53</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/glutathione/Glutathione-1500mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="H61" t="n">
+        <v>99.568</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/semax/Semax-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>99.33499999999999</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/sermorelin/Sermorelin-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H63" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-353561-SteriGenix.pdf</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Unique product/strength/date/report record</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:V63"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10.41</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.33499999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confirmed: Sermorelin (LC-MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lyophilized Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Endotoxin Safety Screen</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Microbial Sterility Screen</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>No Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Heavy Metals</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Arsenic, Cadmium, Lead, Mercury: Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Vial 1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>99.266% purity / 10.31 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Vial 2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>99.403% purity / 10.51 mg</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/sermorelin/Sermorelin-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B28"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>COA ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Compound Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report/Task #</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Verification Key</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Batch/Lot</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Labeled Qty (mg)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Actual Content (mg)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>52.48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variance (mg)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.0496</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Purity %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>99.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confirmed: GHK-Cu (Copper Peptide) (LC-MS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lyophilized</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Appearance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Blue Powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Molecular Formula</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>C14H23CuN6O4+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Molecular Weight</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>402.92 g/mol — Matches</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CAS Number</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>89030-95-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Endotoxin</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Microbial Sterility Screen</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>No Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Heavy Metals</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lead, Cadmium, Arsenic, Mercury: Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Batch Conformity</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Not Tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cap Color</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Crimp Color</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Closure Notes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pass/Fail</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-353561-SteriGenix.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -29023,7 +33725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34086,7 +38788,652 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="H57" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/tesamorelin/Tesamorelin-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="F58" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+      <c r="H58" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-30mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H59" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1478.47</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-21.53</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+      <c r="H60" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/glutathione/Glutathione-1500mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="H61" t="n">
+        <v>99.568</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/semax/Semax-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>99.33499999999999</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/sermorelin/Sermorelin-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="H63" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-353561-SteriGenix.pdf</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:T63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34097,7 +39444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39440,7 +44787,687 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>COA-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Tesamorelin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/tesamorelin/Tesamorelin-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="M57" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.79%; net peptide content 12.18 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>COA-0057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-30mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>30</v>
+      </c>
+      <c r="J58" t="n">
+        <v>37.37</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.2456666666666667</v>
+      </c>
+      <c r="M58" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.86%; net peptide content 37.37 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>COA-0058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Retatrutide</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GLP-1 / Weight</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pristin Biotech</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/pristin-biotech/retatrutide/Retatrutide-10mg-2026-09-01-Pristin.pdf</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M59" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Overfilled</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>20260822</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Identity detected by LCMS/MS; HPLC purity 99.83%; net peptide content 10.80 mg measured by nitrogen quantification using an elemental analyzer. White powder; received 2026-08-29 and analyzed 2026-09-01.</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Not Listed</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Closure colors are not listed or visible in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>COA-0059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Glutathione</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Antioxidant / Cellular Support</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/glutathione/Glutathione-1500mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1478.47</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-21.53</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-0.01435333333333333</v>
+      </c>
+      <c r="M60" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>GLUTATI1500-2608-01-RED-SLV</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Glutathione by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.246% / 1464.59 mg; vial 2: 99.781% / 1492.36 mg.</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Red flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>COA-0060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Semax</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Nootropic / Research</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/semax/Semax-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>10</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="M61" t="n">
+        <v>99.568</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SMX10-2608-01-BLK-SLV</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Semax by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.328% / 9.56 mg; vial 2: 99.808% / 9.74 mg.</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Black flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>COA-0061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sermorelin</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Growth Hormone Support</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kovera Labs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Redacted</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>assets/coa/images/kovera-labs/sermorelin/Sermorelin-10mg-2026-08-18-Kovera.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>10</v>
+      </c>
+      <c r="J62" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="M62" t="n">
+        <v>99.33499999999999</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>SERMOR10-2608-01-GRN-SLV</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Identity confirmed as Sermorelin by LC-MS. Endotoxin PASS; microbial sterility: No Growth; arsenic, cadmium, lead, and mercury Negative. Vial 1: 99.266% / 10.31 mg; vial 2: 99.403% / 10.51 mg.</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Green flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>COA-0062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>GHK-Cu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Cosmetic / Recovery</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>SteriGenix</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RPT-2026-353561</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SGX-VP-2026-0812-U80</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>assets/coa/documents/sterigenix/ghk-cu/COA-RPT-2026-353561-SteriGenix.pdf</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>50</v>
+      </c>
+      <c r="J63" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="M63" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>On label</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>CU260725A</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Identity confirmed as GHK-Cu (Copper Peptide) by LC-MS. Blue lyophilized powder; molecular weight matched 402.92 g/mol. Endotoxin PASS; microbial sterility: No Growth; lead, cadmium, arsenic, and mercury Negative. Batch conformity was not tested.</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Blue flip-off cap with silver aluminum crimp, as listed in the COA.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:U63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
